--- a/model/Output_Budget/1. Baseline/Grid Search/Output Files/1750000/Output_0_9.xlsx
+++ b/model/Output_Budget/1. Baseline/Grid Search/Output Files/1750000/Output_0_9.xlsx
@@ -496,7 +496,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>320071.4256334111</v>
+        <v>320074.8015362156</v>
       </c>
     </row>
     <row r="7">
@@ -506,7 +506,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2995127.424547407</v>
+        <v>2995243.613506387</v>
       </c>
     </row>
     <row r="8">
@@ -516,7 +516,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>20355556.36745723</v>
+        <v>20355670.24425593</v>
       </c>
     </row>
     <row r="9">
@@ -536,7 +536,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>4812396.678818937</v>
+        <v>4812058.022867889</v>
       </c>
     </row>
     <row r="11">
@@ -1120,10 +1120,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="C8" t="n">
-        <v>12.91010078545518</v>
+        <v>0</v>
       </c>
       <c r="D8" t="n">
         <v>0</v>
@@ -1132,7 +1132,7 @@
         <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
@@ -1144,7 +1144,7 @@
         <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>0</v>
+        <v>11.94928935461252</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
@@ -1168,7 +1168,7 @@
         <v>9.990699214544804</v>
       </c>
       <c r="R8" t="n">
-        <v>26</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="S8" t="n">
         <v>0</v>
@@ -1183,13 +1183,13 @@
         <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>0.6263639150735093</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
     </row>
     <row r="9">
@@ -1211,16 +1211,16 @@
         <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>22.15420867374215</v>
+        <v>21.81976115797297</v>
       </c>
       <c r="G9" t="n">
-        <v>26</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="H9" t="n">
-        <v>26</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="I9" t="n">
-        <v>26</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="J9" t="n">
         <v>0.7465913262578567</v>
@@ -1293,19 +1293,19 @@
         <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>0.27419204266741</v>
+        <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>22.26949182588285</v>
+        <v>0</v>
       </c>
       <c r="L10" t="n">
         <v>0</v>
@@ -1320,19 +1320,19 @@
         <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>2.721440735106512</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>19.84491174912431</v>
       </c>
       <c r="U10" t="n">
         <v>0</v>
@@ -1366,22 +1366,22 @@
         <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="F11" t="n">
-        <v>0.9608114308426601</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="G11" t="n">
-        <v>26</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="H11" t="n">
-        <v>26</v>
+        <v>22.56635248423083</v>
       </c>
       <c r="I11" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>11.94928935461252</v>
+        <v>0</v>
       </c>
       <c r="K11" t="n">
         <v>0</v>
@@ -1402,7 +1402,7 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>9.990699214544804</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
         <v>0</v>
@@ -1448,16 +1448,16 @@
         <v>0</v>
       </c>
       <c r="F12" t="n">
-        <v>0</v>
+        <v>21.81976115797297</v>
       </c>
       <c r="G12" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="H12" t="n">
-        <v>22.15420867374214</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="I12" t="n">
-        <v>26</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="J12" t="n">
         <v>0.7465913262578567</v>
@@ -1484,10 +1484,10 @@
         <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="T12" t="n">
         <v>0</v>
@@ -1560,16 +1560,16 @@
         <v>2.721440735106512</v>
       </c>
       <c r="Q13" t="n">
-        <v>26</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="R13" t="n">
-        <v>26</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="S13" t="n">
-        <v>26</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="T13" t="n">
-        <v>19.82224313344376</v>
+        <v>19.84491174912431</v>
       </c>
       <c r="U13" t="n">
         <v>0</v>
@@ -1606,19 +1606,19 @@
         <v>0</v>
       </c>
       <c r="F14" t="n">
-        <v>10.95151064538747</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="G14" t="n">
-        <v>26</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="H14" t="n">
-        <v>26</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="I14" t="n">
-        <v>26</v>
+        <v>22.56635248423083</v>
       </c>
       <c r="J14" t="n">
-        <v>11.94928935461252</v>
+        <v>0</v>
       </c>
       <c r="K14" t="n">
         <v>0</v>
@@ -1685,16 +1685,16 @@
         <v>0</v>
       </c>
       <c r="F15" t="n">
-        <v>22.15420867374215</v>
+        <v>21.81976115797297</v>
       </c>
       <c r="G15" t="n">
-        <v>26</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="H15" t="n">
-        <v>26</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="I15" t="n">
-        <v>26</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="J15" t="n">
         <v>0.7465913262578567</v>
@@ -1767,16 +1767,16 @@
         <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>0.2741920426674241</v>
+        <v>0.2968606583479628</v>
       </c>
       <c r="H16" t="n">
-        <v>26</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="I16" t="n">
-        <v>26</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="J16" t="n">
-        <v>26</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="K16" t="n">
         <v>22.26949182588285</v>
@@ -1843,19 +1843,19 @@
         <v>0</v>
       </c>
       <c r="F17" t="n">
-        <v>0</v>
+        <v>12.35200489467393</v>
       </c>
       <c r="G17" t="n">
-        <v>0</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="H17" t="n">
-        <v>0</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="I17" t="n">
-        <v>0</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="J17" t="n">
-        <v>0</v>
+        <v>11.94928935461252</v>
       </c>
       <c r="K17" t="n">
         <v>0</v>
@@ -1876,19 +1876,19 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>9.990699214544804</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="T17" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="U17" t="n">
-        <v>14.67170078545518</v>
+        <v>0</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -1910,10 +1910,10 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>28</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="C18" t="n">
-        <v>24.66239999999999</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
         <v>0</v>
@@ -1958,16 +1958,16 @@
         <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>28</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="S18" t="n">
         <v>0</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>24.30129424928645</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -1976,7 +1976,7 @@
         <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="Y18" t="n">
         <v>0</v>
@@ -2034,25 +2034,25 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>22.02246762618612</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>28</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>22.44875936050941</v>
       </c>
       <c r="V19" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
         <v>0</v>
@@ -2068,7 +2068,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0</v>
+        <v>200.3360962888296</v>
       </c>
       <c r="C20" t="n">
         <v>0</v>
@@ -2077,13 +2077,13 @@
         <v>0</v>
       </c>
       <c r="E20" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="F20" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="G20" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="H20" t="n">
         <v>0</v>
@@ -2092,7 +2092,7 @@
         <v>0</v>
       </c>
       <c r="J20" t="n">
-        <v>0</v>
+        <v>11.94928935461252</v>
       </c>
       <c r="K20" t="n">
         <v>0</v>
@@ -2131,13 +2131,13 @@
         <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="Y20" t="n">
-        <v>212.2728</v>
+        <v>241.0142888776591</v>
       </c>
     </row>
     <row r="21">
@@ -2147,31 +2147,31 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0</v>
+        <v>166.5331836498673</v>
       </c>
       <c r="C21" t="n">
-        <v>0</v>
+        <v>172.7084989883157</v>
       </c>
       <c r="D21" t="n">
-        <v>0</v>
+        <v>147.4450655646388</v>
       </c>
       <c r="E21" t="n">
         <v>0</v>
       </c>
       <c r="F21" t="n">
-        <v>0</v>
+        <v>145.0692123933839</v>
       </c>
       <c r="G21" t="n">
-        <v>0</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="H21" t="n">
-        <v>0</v>
+        <v>76.08555033932988</v>
       </c>
       <c r="I21" t="n">
-        <v>0</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="J21" t="n">
-        <v>0</v>
+        <v>0.7465913262578567</v>
       </c>
       <c r="K21" t="n">
         <v>0</v>
@@ -2204,19 +2204,19 @@
         <v>0</v>
       </c>
       <c r="U21" t="n">
-        <v>50.01653186979276</v>
+        <v>0</v>
       </c>
       <c r="V21" t="n">
-        <v>232.8005871494253</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>205.7729852034775</v>
+        <v>0</v>
       </c>
       <c r="Y21" t="n">
-        <v>205.6826957773044</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -2280,10 +2280,10 @@
         <v>0</v>
       </c>
       <c r="T22" t="n">
-        <v>0</v>
+        <v>133.186967585368</v>
       </c>
       <c r="U22" t="n">
-        <v>133.186967585368</v>
+        <v>0</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -2305,22 +2305,22 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="C23" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="D23" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="E23" t="n">
         <v>0</v>
       </c>
       <c r="F23" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="G23" t="n">
-        <v>212.2728</v>
+        <v>0</v>
       </c>
       <c r="H23" t="n">
         <v>0</v>
@@ -2374,7 +2374,7 @@
         <v>0</v>
       </c>
       <c r="Y23" t="n">
-        <v>241</v>
+        <v>212.285385643442</v>
       </c>
     </row>
     <row r="24">
@@ -2387,22 +2387,22 @@
         <v>0</v>
       </c>
       <c r="C24" t="n">
-        <v>0</v>
+        <v>172.7084989883157</v>
       </c>
       <c r="D24" t="n">
-        <v>0</v>
+        <v>147.4450655646388</v>
       </c>
       <c r="E24" t="n">
         <v>0</v>
       </c>
       <c r="F24" t="n">
-        <v>50.0165318697929</v>
+        <v>0</v>
       </c>
       <c r="G24" t="n">
-        <v>0</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="H24" t="n">
-        <v>0</v>
+        <v>39.34788763352459</v>
       </c>
       <c r="I24" t="n">
         <v>0</v>
@@ -2447,10 +2447,10 @@
         <v>232.8005871494253</v>
       </c>
       <c r="W24" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>205.7729852034775</v>
+        <v>0</v>
       </c>
       <c r="Y24" t="n">
         <v>205.6826957773044</v>
@@ -2520,13 +2520,13 @@
         <v>0</v>
       </c>
       <c r="U25" t="n">
-        <v>0</v>
+        <v>133.186967585368</v>
       </c>
       <c r="V25" t="n">
         <v>0</v>
       </c>
       <c r="W25" t="n">
-        <v>133.186967585368</v>
+        <v>0</v>
       </c>
       <c r="X25" t="n">
         <v>0</v>
@@ -2542,19 +2542,19 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="C26" t="n">
         <v>0</v>
       </c>
       <c r="D26" t="n">
-        <v>0</v>
+        <v>70.34400780127524</v>
       </c>
       <c r="E26" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="F26" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
@@ -2587,16 +2587,16 @@
         <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>0</v>
+        <v>9.990699214544804</v>
       </c>
       <c r="R26" t="n">
-        <v>0</v>
+        <v>149.8691179411497</v>
       </c>
       <c r="S26" t="n">
         <v>0</v>
       </c>
       <c r="T26" t="n">
-        <v>0</v>
+        <v>223.0958495641314</v>
       </c>
       <c r="U26" t="n">
         <v>0</v>
@@ -2611,7 +2611,7 @@
         <v>0</v>
       </c>
       <c r="Y26" t="n">
-        <v>212.2728</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27">
@@ -2627,10 +2627,10 @@
         <v>0</v>
       </c>
       <c r="D27" t="n">
-        <v>0</v>
+        <v>110.5627721675628</v>
       </c>
       <c r="E27" t="n">
-        <v>0</v>
+        <v>157.6450804554009</v>
       </c>
       <c r="F27" t="n">
         <v>0</v>
@@ -2645,7 +2645,7 @@
         <v>0</v>
       </c>
       <c r="J27" t="n">
-        <v>0.7465913262578567</v>
+        <v>0</v>
       </c>
       <c r="K27" t="n">
         <v>0</v>
@@ -2678,19 +2678,19 @@
         <v>200.1647286948216</v>
       </c>
       <c r="U27" t="n">
-        <v>81.90579899813852</v>
+        <v>225.9413820809748</v>
       </c>
       <c r="V27" t="n">
         <v>0</v>
       </c>
       <c r="W27" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="X27" t="n">
-        <v>205.7729852034775</v>
+        <v>0</v>
       </c>
       <c r="Y27" t="n">
-        <v>205.6826957773044</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28">
@@ -2779,10 +2779,10 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>212.2728</v>
+        <v>0</v>
       </c>
       <c r="C29" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="D29" t="n">
         <v>0</v>
@@ -2791,13 +2791,13 @@
         <v>0</v>
       </c>
       <c r="F29" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="G29" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="I29" t="n">
         <v>0</v>
@@ -2827,10 +2827,10 @@
         <v>0</v>
       </c>
       <c r="R29" t="n">
-        <v>0</v>
+        <v>149.8691179411497</v>
       </c>
       <c r="S29" t="n">
-        <v>0</v>
+        <v>62.4162677022923</v>
       </c>
       <c r="T29" t="n">
         <v>0</v>
@@ -2845,10 +2845,10 @@
         <v>0</v>
       </c>
       <c r="X29" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="Y29" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30">
@@ -2861,28 +2861,28 @@
         <v>0</v>
       </c>
       <c r="C30" t="n">
-        <v>0</v>
+        <v>172.7084989883157</v>
       </c>
       <c r="D30" t="n">
         <v>0</v>
       </c>
       <c r="E30" t="n">
-        <v>35.36610207477823</v>
+        <v>0</v>
       </c>
       <c r="F30" t="n">
         <v>0</v>
       </c>
       <c r="G30" t="n">
-        <v>0</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="H30" t="n">
-        <v>0</v>
+        <v>112.2354442364965</v>
       </c>
       <c r="I30" t="n">
-        <v>0</v>
+        <v>38.47932453505421</v>
       </c>
       <c r="J30" t="n">
-        <v>0</v>
+        <v>0.7465913262578567</v>
       </c>
       <c r="K30" t="n">
         <v>0</v>
@@ -2912,16 +2912,16 @@
         <v>0</v>
       </c>
       <c r="T30" t="n">
-        <v>200.1647286948216</v>
+        <v>0</v>
       </c>
       <c r="U30" t="n">
-        <v>225.9413820809748</v>
+        <v>0</v>
       </c>
       <c r="V30" t="n">
         <v>232.8005871494253</v>
       </c>
       <c r="W30" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="X30" t="n">
         <v>0</v>
@@ -3034,7 +3034,7 @@
         <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>215</v>
+        <v>215.3939976830282</v>
       </c>
       <c r="I32" t="n">
         <v>0</v>
@@ -3061,28 +3061,28 @@
         <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>0</v>
+        <v>9.990699214544804</v>
       </c>
       <c r="R32" t="n">
-        <v>0</v>
+        <v>149.8691179411497</v>
       </c>
       <c r="S32" t="n">
-        <v>0</v>
+        <v>29.85921600351676</v>
       </c>
       <c r="T32" t="n">
-        <v>0</v>
+        <v>215.3939976830282</v>
       </c>
       <c r="U32" t="n">
-        <v>215</v>
+        <v>215.3939976830282</v>
       </c>
       <c r="V32" t="n">
-        <v>189.372</v>
+        <v>0</v>
       </c>
       <c r="W32" t="n">
         <v>0</v>
       </c>
       <c r="X32" t="n">
-        <v>215</v>
+        <v>0</v>
       </c>
       <c r="Y32" t="n">
         <v>0</v>
@@ -3095,10 +3095,10 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>110.3048436375624</v>
+        <v>0</v>
       </c>
       <c r="C33" t="n">
-        <v>0</v>
+        <v>172.7084989883157</v>
       </c>
       <c r="D33" t="n">
         <v>0</v>
@@ -3107,19 +3107,19 @@
         <v>0</v>
       </c>
       <c r="F33" t="n">
-        <v>145.0692123933839</v>
+        <v>0</v>
       </c>
       <c r="G33" t="n">
-        <v>0</v>
+        <v>131.5001063750227</v>
       </c>
       <c r="H33" t="n">
-        <v>112.2354442364965</v>
+        <v>0</v>
       </c>
       <c r="I33" t="n">
-        <v>89.39663285141508</v>
+        <v>0</v>
       </c>
       <c r="J33" t="n">
-        <v>0</v>
+        <v>0.7465913262578567</v>
       </c>
       <c r="K33" t="n">
         <v>0</v>
@@ -3143,28 +3143,28 @@
         <v>0</v>
       </c>
       <c r="R33" t="n">
-        <v>0</v>
+        <v>100.1578341526431</v>
       </c>
       <c r="S33" t="n">
-        <v>171.6831711038378</v>
+        <v>0</v>
       </c>
       <c r="T33" t="n">
         <v>0</v>
       </c>
       <c r="U33" t="n">
-        <v>0</v>
+        <v>215.3939976830282</v>
       </c>
       <c r="V33" t="n">
         <v>0</v>
       </c>
       <c r="W33" t="n">
-        <v>0</v>
+        <v>215.3939976830282</v>
       </c>
       <c r="X33" t="n">
         <v>0</v>
       </c>
       <c r="Y33" t="n">
-        <v>205.6826957773044</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34">
@@ -3192,13 +3192,13 @@
         <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>39.82778746869524</v>
+        <v>0</v>
       </c>
       <c r="I34" t="n">
         <v>0</v>
       </c>
       <c r="J34" t="n">
-        <v>93.35918011667277</v>
+        <v>0</v>
       </c>
       <c r="K34" t="n">
         <v>0</v>
@@ -3243,7 +3243,7 @@
         <v>0</v>
       </c>
       <c r="Y34" t="n">
-        <v>0</v>
+        <v>133.186967585368</v>
       </c>
     </row>
     <row r="35">
@@ -3253,16 +3253,16 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>189.372</v>
+        <v>0</v>
       </c>
       <c r="C35" t="n">
-        <v>215</v>
+        <v>215.3939976830282</v>
       </c>
       <c r="D35" t="n">
         <v>0</v>
       </c>
       <c r="E35" t="n">
-        <v>215</v>
+        <v>0</v>
       </c>
       <c r="F35" t="n">
         <v>0</v>
@@ -3271,13 +3271,13 @@
         <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>215</v>
+        <v>0</v>
       </c>
       <c r="I35" t="n">
-        <v>0</v>
+        <v>167.7790445900539</v>
       </c>
       <c r="J35" t="n">
-        <v>0</v>
+        <v>11.94928935461252</v>
       </c>
       <c r="K35" t="n">
         <v>0</v>
@@ -3298,7 +3298,7 @@
         <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>0</v>
+        <v>9.990699214544804</v>
       </c>
       <c r="R35" t="n">
         <v>0</v>
@@ -3310,10 +3310,10 @@
         <v>0</v>
       </c>
       <c r="U35" t="n">
-        <v>0</v>
+        <v>215.3939976830282</v>
       </c>
       <c r="V35" t="n">
-        <v>0</v>
+        <v>215.3939976830282</v>
       </c>
       <c r="W35" t="n">
         <v>0</v>
@@ -3338,16 +3338,16 @@
         <v>0</v>
       </c>
       <c r="D36" t="n">
-        <v>0</v>
+        <v>147.4450655646388</v>
       </c>
       <c r="E36" t="n">
-        <v>0</v>
+        <v>157.6450804554009</v>
       </c>
       <c r="F36" t="n">
         <v>0</v>
       </c>
       <c r="G36" t="n">
-        <v>0</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="H36" t="n">
         <v>0</v>
@@ -3356,7 +3356,7 @@
         <v>0</v>
       </c>
       <c r="J36" t="n">
-        <v>0.7465913262578567</v>
+        <v>0</v>
       </c>
       <c r="K36" t="n">
         <v>0</v>
@@ -3386,22 +3386,22 @@
         <v>0</v>
       </c>
       <c r="T36" t="n">
-        <v>188.625408673742</v>
+        <v>0</v>
       </c>
       <c r="U36" t="n">
-        <v>215</v>
+        <v>0</v>
       </c>
       <c r="V36" t="n">
-        <v>215</v>
+        <v>0</v>
       </c>
       <c r="W36" t="n">
-        <v>215</v>
+        <v>215.3939976830282</v>
       </c>
       <c r="X36" t="n">
         <v>0</v>
       </c>
       <c r="Y36" t="n">
-        <v>0</v>
+        <v>178.0733653420174</v>
       </c>
     </row>
     <row r="37">
@@ -3453,13 +3453,13 @@
         <v>0</v>
       </c>
       <c r="P37" t="n">
-        <v>2.721440735106512</v>
+        <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>86.16204325169439</v>
+        <v>0</v>
       </c>
       <c r="R37" t="n">
-        <v>44.30348359856713</v>
+        <v>0</v>
       </c>
       <c r="S37" t="n">
         <v>0</v>
@@ -3474,7 +3474,7 @@
         <v>0</v>
       </c>
       <c r="W37" t="n">
-        <v>0</v>
+        <v>133.186967585368</v>
       </c>
       <c r="X37" t="n">
         <v>0</v>
@@ -3490,10 +3490,10 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>215</v>
+        <v>0</v>
       </c>
       <c r="C38" t="n">
-        <v>189.3719999999999</v>
+        <v>0</v>
       </c>
       <c r="D38" t="n">
         <v>0</v>
@@ -3505,7 +3505,7 @@
         <v>0</v>
       </c>
       <c r="G38" t="n">
-        <v>215</v>
+        <v>0</v>
       </c>
       <c r="H38" t="n">
         <v>0</v>
@@ -3538,28 +3538,28 @@
         <v>0</v>
       </c>
       <c r="R38" t="n">
-        <v>0</v>
+        <v>149.8691179411497</v>
       </c>
       <c r="S38" t="n">
-        <v>0</v>
+        <v>209.0200695862453</v>
       </c>
       <c r="T38" t="n">
         <v>0</v>
       </c>
       <c r="U38" t="n">
-        <v>0</v>
+        <v>215.3939976830282</v>
       </c>
       <c r="V38" t="n">
-        <v>0</v>
+        <v>215.3939976830282</v>
       </c>
       <c r="W38" t="n">
-        <v>0</v>
+        <v>46.22384331484438</v>
       </c>
       <c r="X38" t="n">
         <v>0</v>
       </c>
       <c r="Y38" t="n">
-        <v>215</v>
+        <v>0</v>
       </c>
     </row>
     <row r="39">
@@ -3575,7 +3575,7 @@
         <v>0</v>
       </c>
       <c r="D39" t="n">
-        <v>147.4450655646388</v>
+        <v>0</v>
       </c>
       <c r="E39" t="n">
         <v>0</v>
@@ -3623,22 +3623,22 @@
         <v>0</v>
       </c>
       <c r="T39" t="n">
-        <v>200.1647286948216</v>
+        <v>0</v>
       </c>
       <c r="U39" t="n">
-        <v>0</v>
+        <v>215.3939976830282</v>
       </c>
       <c r="V39" t="n">
-        <v>215</v>
+        <v>215.3939976830282</v>
       </c>
       <c r="W39" t="n">
         <v>0</v>
       </c>
       <c r="X39" t="n">
-        <v>66.07950996323517</v>
+        <v>205.7729852034775</v>
       </c>
       <c r="Y39" t="n">
-        <v>205.6826957773044</v>
+        <v>199.3400456387619</v>
       </c>
     </row>
     <row r="40">
@@ -3690,13 +3690,13 @@
         <v>0</v>
       </c>
       <c r="P40" t="n">
-        <v>2.721440735106512</v>
+        <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>86.16204325169439</v>
+        <v>0</v>
       </c>
       <c r="R40" t="n">
-        <v>44.30348359856713</v>
+        <v>0</v>
       </c>
       <c r="S40" t="n">
         <v>0</v>
@@ -3705,7 +3705,7 @@
         <v>0</v>
       </c>
       <c r="U40" t="n">
-        <v>0</v>
+        <v>133.186967585368</v>
       </c>
       <c r="V40" t="n">
         <v>0</v>
@@ -3727,13 +3727,13 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>213</v>
+        <v>0</v>
       </c>
       <c r="C41" t="n">
-        <v>0</v>
+        <v>213.4242636173429</v>
       </c>
       <c r="D41" t="n">
-        <v>0</v>
+        <v>213.4242636173429</v>
       </c>
       <c r="E41" t="n">
         <v>0</v>
@@ -3742,16 +3742,16 @@
         <v>0</v>
       </c>
       <c r="G41" t="n">
-        <v>187.6104</v>
+        <v>0</v>
       </c>
       <c r="H41" t="n">
-        <v>0</v>
+        <v>213.4242636173429</v>
       </c>
       <c r="I41" t="n">
         <v>0</v>
       </c>
       <c r="J41" t="n">
-        <v>0</v>
+        <v>11.94928935461252</v>
       </c>
       <c r="K41" t="n">
         <v>0</v>
@@ -3772,7 +3772,7 @@
         <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>0</v>
+        <v>9.990699214544804</v>
       </c>
       <c r="R41" t="n">
         <v>0</v>
@@ -3784,16 +3784,16 @@
         <v>0</v>
       </c>
       <c r="U41" t="n">
-        <v>0</v>
+        <v>166.0441028249983</v>
       </c>
       <c r="V41" t="n">
         <v>0</v>
       </c>
       <c r="W41" t="n">
-        <v>213</v>
+        <v>0</v>
       </c>
       <c r="X41" t="n">
-        <v>213</v>
+        <v>0</v>
       </c>
       <c r="Y41" t="n">
         <v>0</v>
@@ -3830,7 +3830,7 @@
         <v>0</v>
       </c>
       <c r="J42" t="n">
-        <v>0.7465913262578567</v>
+        <v>0</v>
       </c>
       <c r="K42" t="n">
         <v>0</v>
@@ -3863,16 +3863,16 @@
         <v>0</v>
       </c>
       <c r="U42" t="n">
-        <v>213</v>
+        <v>213.4242636173429</v>
       </c>
       <c r="V42" t="n">
-        <v>213</v>
+        <v>213.4242636173429</v>
       </c>
       <c r="W42" t="n">
-        <v>213</v>
+        <v>213.4242636173429</v>
       </c>
       <c r="X42" t="n">
-        <v>186.8638086737422</v>
+        <v>187.9840913941556</v>
       </c>
       <c r="Y42" t="n">
         <v>0</v>
@@ -3891,49 +3891,49 @@
         <v>0</v>
       </c>
       <c r="D43" t="n">
+        <v>0</v>
+      </c>
+      <c r="E43" t="n">
+        <v>0</v>
+      </c>
+      <c r="F43" t="n">
+        <v>0</v>
+      </c>
+      <c r="G43" t="n">
+        <v>0</v>
+      </c>
+      <c r="H43" t="n">
+        <v>0</v>
+      </c>
+      <c r="I43" t="n">
+        <v>0</v>
+      </c>
+      <c r="J43" t="n">
+        <v>0</v>
+      </c>
+      <c r="K43" t="n">
+        <v>0</v>
+      </c>
+      <c r="L43" t="n">
+        <v>0</v>
+      </c>
+      <c r="M43" t="n">
+        <v>0</v>
+      </c>
+      <c r="N43" t="n">
+        <v>0</v>
+      </c>
+      <c r="O43" t="n">
+        <v>0</v>
+      </c>
+      <c r="P43" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q43" t="n">
+        <v>0</v>
+      </c>
+      <c r="R43" t="n">
         <v>133.186967585368</v>
-      </c>
-      <c r="E43" t="n">
-        <v>0</v>
-      </c>
-      <c r="F43" t="n">
-        <v>0</v>
-      </c>
-      <c r="G43" t="n">
-        <v>0</v>
-      </c>
-      <c r="H43" t="n">
-        <v>0</v>
-      </c>
-      <c r="I43" t="n">
-        <v>0</v>
-      </c>
-      <c r="J43" t="n">
-        <v>0</v>
-      </c>
-      <c r="K43" t="n">
-        <v>0</v>
-      </c>
-      <c r="L43" t="n">
-        <v>0</v>
-      </c>
-      <c r="M43" t="n">
-        <v>0</v>
-      </c>
-      <c r="N43" t="n">
-        <v>0</v>
-      </c>
-      <c r="O43" t="n">
-        <v>0</v>
-      </c>
-      <c r="P43" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q43" t="n">
-        <v>0</v>
-      </c>
-      <c r="R43" t="n">
-        <v>0</v>
       </c>
       <c r="S43" t="n">
         <v>0</v>
@@ -4763,76 +4763,76 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>41.38313210652039</v>
+        <v>14.11961254265382</v>
       </c>
       <c r="C8" t="n">
-        <v>28.34262626262626</v>
+        <v>14.11961254265382</v>
       </c>
       <c r="D8" t="n">
-        <v>28.34262626262626</v>
+        <v>14.11961254265382</v>
       </c>
       <c r="E8" t="n">
-        <v>28.34262626262626</v>
+        <v>14.11961254265382</v>
       </c>
       <c r="F8" t="n">
-        <v>2.08</v>
+        <v>14.11961254265382</v>
       </c>
       <c r="G8" t="n">
-        <v>2.08</v>
+        <v>14.11961254265382</v>
       </c>
       <c r="H8" t="n">
-        <v>2.08</v>
+        <v>14.11961254265382</v>
       </c>
       <c r="I8" t="n">
-        <v>2.08</v>
+        <v>14.11961254265382</v>
       </c>
       <c r="J8" t="n">
-        <v>2.08</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="K8" t="n">
-        <v>27.82</v>
+        <v>27.41371157825499</v>
       </c>
       <c r="L8" t="n">
-        <v>53.56</v>
+        <v>52.77779986093951</v>
       </c>
       <c r="M8" t="n">
-        <v>78.26000000000001</v>
+        <v>77.1170764958388</v>
       </c>
       <c r="N8" t="n">
-        <v>78.26000000000001</v>
+        <v>77.1170764958388</v>
       </c>
       <c r="O8" t="n">
-        <v>78.26000000000001</v>
+        <v>77.1170764958388</v>
       </c>
       <c r="P8" t="n">
-        <v>104</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="Q8" t="n">
-        <v>93.90838463177292</v>
+        <v>92.38954941029624</v>
       </c>
       <c r="R8" t="n">
-        <v>67.64575836914665</v>
+        <v>66.51046739551762</v>
       </c>
       <c r="S8" t="n">
-        <v>67.64575836914665</v>
+        <v>66.51046739551762</v>
       </c>
       <c r="T8" t="n">
-        <v>67.64575836914665</v>
+        <v>66.51046739551762</v>
       </c>
       <c r="U8" t="n">
-        <v>67.64575836914665</v>
+        <v>66.51046739551762</v>
       </c>
       <c r="V8" t="n">
-        <v>67.64575836914665</v>
+        <v>66.51046739551762</v>
       </c>
       <c r="W8" t="n">
-        <v>67.64575836914665</v>
+        <v>65.87777657221105</v>
       </c>
       <c r="X8" t="n">
-        <v>67.64575836914665</v>
+        <v>39.99869455743244</v>
       </c>
       <c r="Y8" t="n">
-        <v>67.64575836914665</v>
+        <v>14.11961254265382</v>
       </c>
     </row>
     <row r="9">
@@ -4842,76 +4842,76 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>104</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="C9" t="n">
-        <v>104</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="D9" t="n">
-        <v>104</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="E9" t="n">
-        <v>104</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="F9" t="n">
-        <v>81.62201144066449</v>
+        <v>80.44100199269204</v>
       </c>
       <c r="G9" t="n">
-        <v>55.35938517803824</v>
+        <v>54.56191997791342</v>
       </c>
       <c r="H9" t="n">
-        <v>29.09675891541198</v>
+        <v>28.6828379631348</v>
       </c>
       <c r="I9" t="n">
-        <v>2.834132652785714</v>
+        <v>2.80375594835618</v>
       </c>
       <c r="J9" t="n">
-        <v>2.08</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="K9" t="n">
-        <v>26.78000000000001</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="L9" t="n">
-        <v>26.78000000000001</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="M9" t="n">
-        <v>26.78000000000001</v>
+        <v>27.41371157825499</v>
       </c>
       <c r="N9" t="n">
-        <v>52.52000000000001</v>
+        <v>27.41371157825499</v>
       </c>
       <c r="O9" t="n">
-        <v>78.26000000000001</v>
+        <v>51.75298821315428</v>
       </c>
       <c r="P9" t="n">
-        <v>78.26000000000001</v>
+        <v>77.1170764958388</v>
       </c>
       <c r="Q9" t="n">
-        <v>104</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="R9" t="n">
-        <v>104</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="S9" t="n">
-        <v>104</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="T9" t="n">
-        <v>104</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="U9" t="n">
-        <v>104</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="V9" t="n">
-        <v>104</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="W9" t="n">
-        <v>104</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="X9" t="n">
-        <v>104</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="Y9" t="n">
-        <v>104</v>
+        <v>102.4811647785233</v>
       </c>
     </row>
     <row r="10">
@@ -4921,76 +4921,76 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>103.6392766348993</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="C10" t="n">
-        <v>103.6392766348993</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="D10" t="n">
-        <v>103.6392766348993</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="E10" t="n">
-        <v>103.6392766348993</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="F10" t="n">
-        <v>103.6392766348993</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="G10" t="n">
-        <v>103.3623149756393</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="H10" t="n">
-        <v>77.09968871301299</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="I10" t="n">
-        <v>50.83706245038672</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="J10" t="n">
-        <v>24.57443618776046</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="K10" t="n">
-        <v>2.08</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="L10" t="n">
-        <v>27.82</v>
+        <v>27.41371157825499</v>
       </c>
       <c r="M10" t="n">
-        <v>53.56</v>
+        <v>52.77779986093951</v>
       </c>
       <c r="N10" t="n">
-        <v>79.3</v>
+        <v>78.14188814362403</v>
       </c>
       <c r="O10" t="n">
-        <v>103.6392766348993</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="P10" t="n">
-        <v>103.6392766348993</v>
+        <v>99.73223474306219</v>
       </c>
       <c r="Q10" t="n">
-        <v>103.6392766348993</v>
+        <v>73.85315272828358</v>
       </c>
       <c r="R10" t="n">
-        <v>103.6392766348993</v>
+        <v>47.97407071350496</v>
       </c>
       <c r="S10" t="n">
-        <v>103.6392766348993</v>
+        <v>22.09498869872634</v>
       </c>
       <c r="T10" t="n">
-        <v>103.6392766348993</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="U10" t="n">
-        <v>103.6392766348993</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="V10" t="n">
-        <v>103.6392766348993</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="W10" t="n">
-        <v>103.6392766348993</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="X10" t="n">
-        <v>103.6392766348993</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="Y10" t="n">
-        <v>103.6392766348993</v>
+        <v>2.049623295570466</v>
       </c>
     </row>
     <row r="11">
@@ -5000,76 +5000,76 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>93.90838463177292</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="C11" t="n">
-        <v>93.90838463177292</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="D11" t="n">
-        <v>93.90838463177292</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="E11" t="n">
-        <v>93.90838463177292</v>
+        <v>76.6020827637447</v>
       </c>
       <c r="F11" t="n">
-        <v>92.93786803496215</v>
+        <v>50.72300074896609</v>
       </c>
       <c r="G11" t="n">
-        <v>66.67524177233588</v>
+        <v>24.84391873418747</v>
       </c>
       <c r="H11" t="n">
-        <v>40.41261550970962</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="I11" t="n">
-        <v>14.14998924708335</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="J11" t="n">
-        <v>2.08</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="K11" t="n">
-        <v>2.08</v>
+        <v>27.41371157825499</v>
       </c>
       <c r="L11" t="n">
-        <v>26.78000000000001</v>
+        <v>52.77779986093951</v>
       </c>
       <c r="M11" t="n">
-        <v>26.78000000000001</v>
+        <v>52.77779986093951</v>
       </c>
       <c r="N11" t="n">
-        <v>52.52000000000001</v>
+        <v>52.77779986093951</v>
       </c>
       <c r="O11" t="n">
-        <v>78.26000000000001</v>
+        <v>77.1170764958388</v>
       </c>
       <c r="P11" t="n">
-        <v>104</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="Q11" t="n">
-        <v>93.90838463177292</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="R11" t="n">
-        <v>93.90838463177292</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="S11" t="n">
-        <v>93.90838463177292</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="T11" t="n">
-        <v>93.90838463177292</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="U11" t="n">
-        <v>93.90838463177292</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="V11" t="n">
-        <v>93.90838463177292</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="W11" t="n">
-        <v>93.90838463177292</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="X11" t="n">
-        <v>93.90838463177292</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="Y11" t="n">
-        <v>93.90838463177292</v>
+        <v>102.4811647785233</v>
       </c>
     </row>
     <row r="12">
@@ -5079,76 +5079,76 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>51.47474747474747</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="C12" t="n">
-        <v>51.47474747474747</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="D12" t="n">
-        <v>51.47474747474747</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="E12" t="n">
-        <v>51.47474747474747</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="F12" t="n">
-        <v>51.47474747474747</v>
+        <v>80.44100199269204</v>
       </c>
       <c r="G12" t="n">
-        <v>51.47474747474747</v>
+        <v>54.56191997791342</v>
       </c>
       <c r="H12" t="n">
-        <v>29.09675891541198</v>
+        <v>28.6828379631348</v>
       </c>
       <c r="I12" t="n">
-        <v>2.834132652785714</v>
+        <v>2.80375594835618</v>
       </c>
       <c r="J12" t="n">
-        <v>2.08</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="K12" t="n">
-        <v>2.08</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="L12" t="n">
-        <v>27.82</v>
+        <v>27.41371157825499</v>
       </c>
       <c r="M12" t="n">
-        <v>53.56</v>
+        <v>52.77779986093951</v>
       </c>
       <c r="N12" t="n">
-        <v>79.3</v>
+        <v>52.77779986093951</v>
       </c>
       <c r="O12" t="n">
-        <v>104</v>
+        <v>52.77779986093951</v>
       </c>
       <c r="P12" t="n">
-        <v>104</v>
+        <v>77.1170764958388</v>
       </c>
       <c r="Q12" t="n">
-        <v>104</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="R12" t="n">
-        <v>77.73737373737373</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="S12" t="n">
-        <v>51.47474747474747</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="T12" t="n">
-        <v>51.47474747474747</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="U12" t="n">
-        <v>51.47474747474747</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="V12" t="n">
-        <v>51.47474747474747</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="W12" t="n">
-        <v>51.47474747474747</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="X12" t="n">
-        <v>51.47474747474747</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="Y12" t="n">
-        <v>51.47474747474747</v>
+        <v>102.4811647785233</v>
       </c>
     </row>
     <row r="13">
@@ -5158,76 +5158,76 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2.08</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="C13" t="n">
-        <v>2.08</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="D13" t="n">
-        <v>2.08</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="E13" t="n">
-        <v>2.08</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="F13" t="n">
-        <v>2.08</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="G13" t="n">
-        <v>2.08</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="H13" t="n">
-        <v>2.08</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="I13" t="n">
-        <v>2.08</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="J13" t="n">
-        <v>2.08</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="K13" t="n">
-        <v>2.08</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="L13" t="n">
-        <v>27.82</v>
+        <v>27.41371157825499</v>
       </c>
       <c r="M13" t="n">
-        <v>53.56</v>
+        <v>52.77779986093951</v>
       </c>
       <c r="N13" t="n">
-        <v>79.3</v>
+        <v>78.14188814362404</v>
       </c>
       <c r="O13" t="n">
-        <v>103.6392766348993</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="P13" t="n">
-        <v>100.8903465994381</v>
+        <v>99.73223474306219</v>
       </c>
       <c r="Q13" t="n">
-        <v>74.62772033681188</v>
+        <v>73.85315272828358</v>
       </c>
       <c r="R13" t="n">
-        <v>48.36509407418561</v>
+        <v>47.97407071350496</v>
       </c>
       <c r="S13" t="n">
-        <v>22.10246781155935</v>
+        <v>22.09498869872634</v>
       </c>
       <c r="T13" t="n">
-        <v>2.08</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="U13" t="n">
-        <v>2.08</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="V13" t="n">
-        <v>2.08</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="W13" t="n">
-        <v>2.08</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="X13" t="n">
-        <v>2.08</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="Y13" t="n">
-        <v>2.08</v>
+        <v>2.049623295570466</v>
       </c>
     </row>
     <row r="14">
@@ -5237,76 +5237,76 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>104</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="C14" t="n">
-        <v>104</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="D14" t="n">
-        <v>104</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="E14" t="n">
-        <v>104</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="F14" t="n">
-        <v>92.93786803496215</v>
+        <v>76.6020827637447</v>
       </c>
       <c r="G14" t="n">
-        <v>66.67524177233588</v>
+        <v>50.72300074896609</v>
       </c>
       <c r="H14" t="n">
-        <v>40.41261550970962</v>
+        <v>24.84391873418747</v>
       </c>
       <c r="I14" t="n">
-        <v>14.14998924708335</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="J14" t="n">
-        <v>2.08</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="K14" t="n">
-        <v>2.08</v>
+        <v>27.41371157825499</v>
       </c>
       <c r="L14" t="n">
-        <v>27.82</v>
+        <v>52.77779986093951</v>
       </c>
       <c r="M14" t="n">
-        <v>53.56</v>
+        <v>77.1170764958388</v>
       </c>
       <c r="N14" t="n">
-        <v>78.26000000000001</v>
+        <v>77.1170764958388</v>
       </c>
       <c r="O14" t="n">
-        <v>104</v>
+        <v>77.1170764958388</v>
       </c>
       <c r="P14" t="n">
-        <v>104</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="Q14" t="n">
-        <v>104</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="R14" t="n">
-        <v>104</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="S14" t="n">
-        <v>104</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="T14" t="n">
-        <v>104</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="U14" t="n">
-        <v>104</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="V14" t="n">
-        <v>104</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="W14" t="n">
-        <v>104</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="X14" t="n">
-        <v>104</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="Y14" t="n">
-        <v>104</v>
+        <v>102.4811647785233</v>
       </c>
     </row>
     <row r="15">
@@ -5316,76 +5316,76 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>104</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="C15" t="n">
-        <v>104</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="D15" t="n">
-        <v>104</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="E15" t="n">
-        <v>104</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="F15" t="n">
-        <v>81.62201144066449</v>
+        <v>80.44100199269204</v>
       </c>
       <c r="G15" t="n">
-        <v>55.35938517803824</v>
+        <v>54.56191997791342</v>
       </c>
       <c r="H15" t="n">
-        <v>29.09675891541198</v>
+        <v>28.6828379631348</v>
       </c>
       <c r="I15" t="n">
-        <v>2.834132652785714</v>
+        <v>2.80375594835618</v>
       </c>
       <c r="J15" t="n">
-        <v>2.08</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="K15" t="n">
-        <v>26.78000000000001</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="L15" t="n">
-        <v>26.78000000000001</v>
+        <v>27.41371157825499</v>
       </c>
       <c r="M15" t="n">
-        <v>26.78000000000001</v>
+        <v>52.77779986093951</v>
       </c>
       <c r="N15" t="n">
-        <v>52.52000000000001</v>
+        <v>52.77779986093951</v>
       </c>
       <c r="O15" t="n">
-        <v>78.26000000000001</v>
+        <v>52.77779986093951</v>
       </c>
       <c r="P15" t="n">
-        <v>104</v>
+        <v>77.1170764958388</v>
       </c>
       <c r="Q15" t="n">
-        <v>104</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="R15" t="n">
-        <v>104</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="S15" t="n">
-        <v>104</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="T15" t="n">
-        <v>104</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="U15" t="n">
-        <v>104</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="V15" t="n">
-        <v>104</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="W15" t="n">
-        <v>104</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="X15" t="n">
-        <v>104</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="Y15" t="n">
-        <v>104</v>
+        <v>102.4811647785233</v>
       </c>
     </row>
     <row r="16">
@@ -5395,76 +5395,76 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>104</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="C16" t="n">
-        <v>104</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="D16" t="n">
-        <v>104</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="E16" t="n">
-        <v>104</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="F16" t="n">
-        <v>104</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="G16" t="n">
-        <v>103.72303834074</v>
+        <v>102.1813055276668</v>
       </c>
       <c r="H16" t="n">
-        <v>77.46041207811371</v>
+        <v>76.30222351288816</v>
       </c>
       <c r="I16" t="n">
-        <v>51.19778581548745</v>
+        <v>50.42314149810954</v>
       </c>
       <c r="J16" t="n">
-        <v>24.93515955286119</v>
+        <v>24.54405948333093</v>
       </c>
       <c r="K16" t="n">
-        <v>2.44072336510073</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="L16" t="n">
-        <v>28.18072336510073</v>
+        <v>27.41371157825499</v>
       </c>
       <c r="M16" t="n">
-        <v>53.92072336510073</v>
+        <v>52.77779986093951</v>
       </c>
       <c r="N16" t="n">
-        <v>79.66072336510072</v>
+        <v>78.14188814362403</v>
       </c>
       <c r="O16" t="n">
-        <v>104</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="P16" t="n">
-        <v>104</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="Q16" t="n">
-        <v>104</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="R16" t="n">
-        <v>104</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="S16" t="n">
-        <v>104</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="T16" t="n">
-        <v>104</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="U16" t="n">
-        <v>104</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="V16" t="n">
-        <v>104</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="W16" t="n">
-        <v>104</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="X16" t="n">
-        <v>104</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="Y16" t="n">
-        <v>104</v>
+        <v>102.4811647785233</v>
       </c>
     </row>
     <row r="17">
@@ -5474,76 +5474,76 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2.24</v>
+        <v>110.3601010412646</v>
       </c>
       <c r="C17" t="n">
-        <v>2.24</v>
+        <v>110.3601010412646</v>
       </c>
       <c r="D17" t="n">
-        <v>2.24</v>
+        <v>110.3601010412646</v>
       </c>
       <c r="E17" t="n">
-        <v>2.24</v>
+        <v>110.3601010412646</v>
       </c>
       <c r="F17" t="n">
-        <v>2.24</v>
+        <v>97.8833284203818</v>
       </c>
       <c r="G17" t="n">
-        <v>2.24</v>
+        <v>70.01461603622408</v>
       </c>
       <c r="H17" t="n">
-        <v>2.24</v>
+        <v>42.14590365206637</v>
       </c>
       <c r="I17" t="n">
-        <v>2.24</v>
+        <v>14.27719126790864</v>
       </c>
       <c r="J17" t="n">
-        <v>2.24</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="K17" t="n">
-        <v>29.96</v>
+        <v>29.52132702853827</v>
       </c>
       <c r="L17" t="n">
-        <v>56.56</v>
+        <v>56.83545203625125</v>
       </c>
       <c r="M17" t="n">
-        <v>56.56</v>
+        <v>84.14957704396423</v>
       </c>
       <c r="N17" t="n">
-        <v>56.56</v>
+        <v>110.3601010412646</v>
       </c>
       <c r="O17" t="n">
-        <v>84.28</v>
+        <v>110.3601010412646</v>
       </c>
       <c r="P17" t="n">
-        <v>112</v>
+        <v>110.3601010412646</v>
       </c>
       <c r="Q17" t="n">
-        <v>101.9083846317729</v>
+        <v>110.3601010412646</v>
       </c>
       <c r="R17" t="n">
-        <v>73.62555634894463</v>
+        <v>110.3601010412646</v>
       </c>
       <c r="S17" t="n">
-        <v>45.34272806611634</v>
+        <v>110.3601010412646</v>
       </c>
       <c r="T17" t="n">
-        <v>17.05989978328806</v>
+        <v>110.3601010412646</v>
       </c>
       <c r="U17" t="n">
-        <v>2.24</v>
+        <v>110.3601010412646</v>
       </c>
       <c r="V17" t="n">
-        <v>2.24</v>
+        <v>110.3601010412646</v>
       </c>
       <c r="W17" t="n">
-        <v>2.24</v>
+        <v>110.3601010412646</v>
       </c>
       <c r="X17" t="n">
-        <v>2.24</v>
+        <v>110.3601010412646</v>
       </c>
       <c r="Y17" t="n">
-        <v>2.24</v>
+        <v>110.3601010412646</v>
       </c>
     </row>
     <row r="18">
@@ -5553,76 +5553,76 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>27.15151515151514</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="C18" t="n">
-        <v>2.24</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="D18" t="n">
-        <v>2.24</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="E18" t="n">
-        <v>2.24</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="F18" t="n">
-        <v>2.24</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="G18" t="n">
-        <v>2.24</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="H18" t="n">
-        <v>2.24</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="I18" t="n">
-        <v>2.24</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="J18" t="n">
-        <v>2.24</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="K18" t="n">
-        <v>29.96</v>
+        <v>29.52132702853827</v>
       </c>
       <c r="L18" t="n">
-        <v>57.68</v>
+        <v>29.52132702853827</v>
       </c>
       <c r="M18" t="n">
-        <v>84.28</v>
+        <v>29.52132702853827</v>
       </c>
       <c r="N18" t="n">
-        <v>84.28</v>
+        <v>56.83545203625125</v>
       </c>
       <c r="O18" t="n">
-        <v>84.28</v>
+        <v>84.14957704396423</v>
       </c>
       <c r="P18" t="n">
-        <v>84.28</v>
+        <v>110.3601010412646</v>
       </c>
       <c r="Q18" t="n">
-        <v>112</v>
+        <v>110.3601010412646</v>
       </c>
       <c r="R18" t="n">
-        <v>83.71717171717171</v>
+        <v>82.49138865710684</v>
       </c>
       <c r="S18" t="n">
-        <v>83.71717171717171</v>
+        <v>82.49138865710684</v>
       </c>
       <c r="T18" t="n">
-        <v>83.71717171717171</v>
+        <v>57.94462678914073</v>
       </c>
       <c r="U18" t="n">
-        <v>83.71717171717171</v>
+        <v>30.07591440498301</v>
       </c>
       <c r="V18" t="n">
-        <v>83.71717171717171</v>
+        <v>30.07591440498301</v>
       </c>
       <c r="W18" t="n">
-        <v>83.71717171717171</v>
+        <v>30.07591440498301</v>
       </c>
       <c r="X18" t="n">
-        <v>55.43434343434343</v>
+        <v>30.07591440498301</v>
       </c>
       <c r="Y18" t="n">
-        <v>55.43434343434343</v>
+        <v>30.07591440498301</v>
       </c>
     </row>
     <row r="19">
@@ -5632,76 +5632,76 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>2.24</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="C19" t="n">
-        <v>2.24</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="D19" t="n">
-        <v>2.24</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="E19" t="n">
-        <v>2.24</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="F19" t="n">
-        <v>2.24</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="G19" t="n">
-        <v>2.24</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="H19" t="n">
-        <v>2.24</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="I19" t="n">
-        <v>2.24</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="J19" t="n">
-        <v>2.24</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="K19" t="n">
-        <v>2.24</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="L19" t="n">
-        <v>29.55412500771298</v>
+        <v>29.52132702853827</v>
       </c>
       <c r="M19" t="n">
-        <v>57.27412500771297</v>
+        <v>56.83545203625125</v>
       </c>
       <c r="N19" t="n">
-        <v>84.99412500771297</v>
+        <v>84.14957704396423</v>
       </c>
       <c r="O19" t="n">
-        <v>109.3334016426122</v>
+        <v>108.4888536788635</v>
       </c>
       <c r="P19" t="n">
-        <v>109.3334016426122</v>
+        <v>108.4888536788635</v>
       </c>
       <c r="Q19" t="n">
-        <v>87.08848484848485</v>
+        <v>108.4888536788635</v>
       </c>
       <c r="R19" t="n">
-        <v>58.80565656565657</v>
+        <v>80.62014129470579</v>
       </c>
       <c r="S19" t="n">
-        <v>58.80565656565657</v>
+        <v>52.75142891054807</v>
       </c>
       <c r="T19" t="n">
-        <v>58.80565656565657</v>
+        <v>24.88271652639035</v>
       </c>
       <c r="U19" t="n">
-        <v>58.80565656565657</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="V19" t="n">
-        <v>30.52282828282829</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="W19" t="n">
-        <v>2.24</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="X19" t="n">
-        <v>2.24</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="Y19" t="n">
-        <v>2.24</v>
+        <v>2.207202020825291</v>
       </c>
     </row>
     <row r="20">
@@ -5711,76 +5711,76 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>749.5830303030303</v>
+        <v>31.35113235729608</v>
       </c>
       <c r="C20" t="n">
-        <v>749.5830303030303</v>
+        <v>31.35113235729608</v>
       </c>
       <c r="D20" t="n">
-        <v>749.5830303030303</v>
+        <v>31.35113235729608</v>
       </c>
       <c r="E20" t="n">
-        <v>506.1486868686869</v>
+        <v>31.35113235729608</v>
       </c>
       <c r="F20" t="n">
-        <v>262.7143434343434</v>
+        <v>31.35113235729608</v>
       </c>
       <c r="G20" t="n">
-        <v>19.28</v>
+        <v>31.35113235729608</v>
       </c>
       <c r="H20" t="n">
-        <v>19.28</v>
+        <v>31.35113235729608</v>
       </c>
       <c r="I20" t="n">
-        <v>19.28</v>
+        <v>31.35113235729608</v>
       </c>
       <c r="J20" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K20" t="n">
-        <v>122.2389935104989</v>
+        <v>122.2961490211351</v>
       </c>
       <c r="L20" t="n">
-        <v>302.3148450951575</v>
+        <v>302.3720006057937</v>
       </c>
       <c r="M20" t="n">
-        <v>519.2904723580616</v>
+        <v>519.3476278686978</v>
       </c>
       <c r="N20" t="n">
-        <v>725.144994565301</v>
+        <v>725.2021500759372</v>
       </c>
       <c r="O20" t="n">
-        <v>874.339944707949</v>
+        <v>874.3971002185853</v>
       </c>
       <c r="P20" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Q20" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="R20" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="S20" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="T20" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="U20" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="V20" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="W20" t="n">
-        <v>964</v>
+        <v>720.6083788665362</v>
       </c>
       <c r="X20" t="n">
-        <v>964</v>
+        <v>477.1596022224361</v>
       </c>
       <c r="Y20" t="n">
-        <v>749.5830303030303</v>
+        <v>233.7108255783361</v>
       </c>
     </row>
     <row r="21">
@@ -5790,76 +5790,76 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>19.28</v>
+        <v>795.8418184905681</v>
       </c>
       <c r="C21" t="n">
-        <v>19.28</v>
+        <v>621.3887892094411</v>
       </c>
       <c r="D21" t="n">
-        <v>19.28</v>
+        <v>472.4543795481899</v>
       </c>
       <c r="E21" t="n">
-        <v>19.28</v>
+        <v>472.4543795481899</v>
       </c>
       <c r="F21" t="n">
-        <v>19.28</v>
+        <v>325.9198215750748</v>
       </c>
       <c r="G21" t="n">
-        <v>19.28</v>
+        <v>187.1889961576903</v>
       </c>
       <c r="H21" t="n">
-        <v>19.28</v>
+        <v>110.334904905842</v>
       </c>
       <c r="I21" t="n">
-        <v>19.28</v>
+        <v>20.03527576299844</v>
       </c>
       <c r="J21" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K21" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="L21" t="n">
-        <v>19.28</v>
+        <v>249.2442489785619</v>
       </c>
       <c r="M21" t="n">
-        <v>234.7819638733197</v>
+        <v>487.8483949674443</v>
       </c>
       <c r="N21" t="n">
-        <v>473.3719638733197</v>
+        <v>725.4530095217538</v>
       </c>
       <c r="O21" t="n">
-        <v>711.9619638733197</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="P21" t="n">
-        <v>894.6054414866707</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Q21" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="R21" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="S21" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="T21" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="U21" t="n">
-        <v>913.478250636573</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="V21" t="n">
-        <v>678.3261424048302</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="W21" t="n">
-        <v>434.8917989704868</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="X21" t="n">
-        <v>227.0402987649539</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Y21" t="n">
-        <v>19.28</v>
+        <v>964.0571555106362</v>
       </c>
     </row>
     <row r="22">
@@ -5869,76 +5869,76 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>829.4677095097293</v>
+        <v>829.5248650203655</v>
       </c>
       <c r="C22" t="n">
-        <v>829.4677095097293</v>
+        <v>829.5248650203655</v>
       </c>
       <c r="D22" t="n">
-        <v>829.4677095097293</v>
+        <v>829.5248650203655</v>
       </c>
       <c r="E22" t="n">
-        <v>829.4677095097293</v>
+        <v>829.5248650203655</v>
       </c>
       <c r="F22" t="n">
-        <v>829.4677095097293</v>
+        <v>829.5248650203655</v>
       </c>
       <c r="G22" t="n">
-        <v>829.4677095097293</v>
+        <v>829.5248650203655</v>
       </c>
       <c r="H22" t="n">
-        <v>829.4677095097293</v>
+        <v>829.5248650203655</v>
       </c>
       <c r="I22" t="n">
-        <v>829.4677095097293</v>
+        <v>829.5248650203655</v>
       </c>
       <c r="J22" t="n">
-        <v>829.4677095097293</v>
+        <v>829.5248650203655</v>
       </c>
       <c r="K22" t="n">
-        <v>829.4677095097293</v>
+        <v>829.5248650203655</v>
       </c>
       <c r="L22" t="n">
-        <v>856.7818345174422</v>
+        <v>856.8389900280785</v>
       </c>
       <c r="M22" t="n">
-        <v>895.9698727096644</v>
+        <v>896.0270282203006</v>
       </c>
       <c r="N22" t="n">
-        <v>939.6607233651007</v>
+        <v>939.7178788757369</v>
       </c>
       <c r="O22" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="P22" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Q22" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="R22" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="S22" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="T22" t="n">
-        <v>964</v>
+        <v>829.5248650203655</v>
       </c>
       <c r="U22" t="n">
-        <v>829.4677095097293</v>
+        <v>829.5248650203655</v>
       </c>
       <c r="V22" t="n">
-        <v>829.4677095097293</v>
+        <v>829.5248650203655</v>
       </c>
       <c r="W22" t="n">
-        <v>829.4677095097293</v>
+        <v>829.5248650203655</v>
       </c>
       <c r="X22" t="n">
-        <v>829.4677095097293</v>
+        <v>829.5248650203655</v>
       </c>
       <c r="Y22" t="n">
-        <v>829.4677095097293</v>
+        <v>829.5248650203655</v>
       </c>
     </row>
     <row r="23">
@@ -5948,76 +5948,76 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>477.1313131313132</v>
+        <v>749.627473042513</v>
       </c>
       <c r="C23" t="n">
-        <v>477.1313131313132</v>
+        <v>506.1786963984129</v>
       </c>
       <c r="D23" t="n">
-        <v>477.1313131313132</v>
+        <v>262.7299197543128</v>
       </c>
       <c r="E23" t="n">
-        <v>477.1313131313132</v>
+        <v>262.7299197543128</v>
       </c>
       <c r="F23" t="n">
-        <v>233.6969696969697</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="G23" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="H23" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="I23" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J23" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K23" t="n">
-        <v>122.2389935104989</v>
+        <v>122.2961490211351</v>
       </c>
       <c r="L23" t="n">
-        <v>302.3148450951575</v>
+        <v>302.3720006057937</v>
       </c>
       <c r="M23" t="n">
-        <v>519.2904723580616</v>
+        <v>519.3476278686978</v>
       </c>
       <c r="N23" t="n">
-        <v>725.144994565301</v>
+        <v>725.2021500759372</v>
       </c>
       <c r="O23" t="n">
-        <v>874.339944707949</v>
+        <v>874.3971002185853</v>
       </c>
       <c r="P23" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Q23" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="R23" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="S23" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="T23" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="U23" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="V23" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="W23" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="X23" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Y23" t="n">
-        <v>720.5656565656566</v>
+        <v>749.627473042513</v>
       </c>
     </row>
     <row r="24">
@@ -6027,76 +6027,76 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>69.80174936342718</v>
+        <v>521.1447485139397</v>
       </c>
       <c r="C24" t="n">
-        <v>69.80174936342718</v>
+        <v>346.6917192328127</v>
       </c>
       <c r="D24" t="n">
-        <v>69.80174936342718</v>
+        <v>197.7573095715614</v>
       </c>
       <c r="E24" t="n">
-        <v>69.80174936342718</v>
+        <v>197.7573095715614</v>
       </c>
       <c r="F24" t="n">
-        <v>19.28</v>
+        <v>197.7573095715614</v>
       </c>
       <c r="G24" t="n">
-        <v>19.28</v>
+        <v>59.02648415417696</v>
       </c>
       <c r="H24" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="I24" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J24" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K24" t="n">
-        <v>144.6375600578374</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="L24" t="n">
-        <v>374.6006659261865</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="M24" t="n">
-        <v>613.1906659261865</v>
+        <v>234.810827406191</v>
       </c>
       <c r="N24" t="n">
-        <v>851.7806659261865</v>
+        <v>473.4149733950735</v>
       </c>
       <c r="O24" t="n">
-        <v>964</v>
+        <v>712.019119383956</v>
       </c>
       <c r="P24" t="n">
-        <v>964</v>
+        <v>894.6625969973069</v>
       </c>
       <c r="Q24" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="R24" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="S24" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="T24" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="U24" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="V24" t="n">
-        <v>728.8478917682573</v>
+        <v>728.9050472788936</v>
       </c>
       <c r="W24" t="n">
-        <v>485.4135483339139</v>
+        <v>728.9050472788936</v>
       </c>
       <c r="X24" t="n">
-        <v>277.5620481283811</v>
+        <v>728.9050472788936</v>
       </c>
       <c r="Y24" t="n">
-        <v>69.80174936342718</v>
+        <v>521.1447485139397</v>
       </c>
     </row>
     <row r="25">
@@ -6106,76 +6106,76 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="C25" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="D25" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="E25" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="F25" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="G25" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="H25" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="I25" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J25" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K25" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="L25" t="n">
-        <v>46.59412500771298</v>
+        <v>46.5952681179257</v>
       </c>
       <c r="M25" t="n">
-        <v>85.78216319993516</v>
+        <v>85.78330631014788</v>
       </c>
       <c r="N25" t="n">
-        <v>129.4730138553714</v>
+        <v>129.4741569655842</v>
       </c>
       <c r="O25" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="P25" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="Q25" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="R25" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="S25" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="T25" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="U25" t="n">
-        <v>153.8122904902707</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="V25" t="n">
-        <v>153.8122904902707</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="W25" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="X25" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="Y25" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
     </row>
     <row r="26">
@@ -6185,76 +6185,76 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>506.1486868686869</v>
+        <v>577.2332497330343</v>
       </c>
       <c r="C26" t="n">
-        <v>506.1486868686869</v>
+        <v>577.2332497330343</v>
       </c>
       <c r="D26" t="n">
-        <v>506.1486868686869</v>
+        <v>506.1786963984129</v>
       </c>
       <c r="E26" t="n">
-        <v>262.7143434343434</v>
+        <v>262.7299197543128</v>
       </c>
       <c r="F26" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="G26" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="H26" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="I26" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J26" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K26" t="n">
-        <v>122.2389935104989</v>
+        <v>122.2961490211351</v>
       </c>
       <c r="L26" t="n">
-        <v>302.3148450951575</v>
+        <v>302.3720006057937</v>
       </c>
       <c r="M26" t="n">
-        <v>519.2904723580616</v>
+        <v>519.3476278686978</v>
       </c>
       <c r="N26" t="n">
-        <v>725.144994565301</v>
+        <v>725.2021500759372</v>
       </c>
       <c r="O26" t="n">
-        <v>874.339944707949</v>
+        <v>874.3971002185853</v>
       </c>
       <c r="P26" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Q26" t="n">
-        <v>964</v>
+        <v>953.9655401424092</v>
       </c>
       <c r="R26" t="n">
-        <v>964</v>
+        <v>802.5825927271064</v>
       </c>
       <c r="S26" t="n">
-        <v>964</v>
+        <v>802.5825927271064</v>
       </c>
       <c r="T26" t="n">
-        <v>964</v>
+        <v>577.2332497330343</v>
       </c>
       <c r="U26" t="n">
-        <v>964</v>
+        <v>577.2332497330343</v>
       </c>
       <c r="V26" t="n">
-        <v>964</v>
+        <v>577.2332497330343</v>
       </c>
       <c r="W26" t="n">
-        <v>964</v>
+        <v>577.2332497330343</v>
       </c>
       <c r="X26" t="n">
-        <v>964</v>
+        <v>577.2332497330343</v>
       </c>
       <c r="Y26" t="n">
-        <v>749.5830303030303</v>
+        <v>577.2332497330343</v>
       </c>
     </row>
     <row r="27">
@@ -6264,76 +6264,76 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>20.03413265278571</v>
+        <v>290.1981659616912</v>
       </c>
       <c r="C27" t="n">
-        <v>20.03413265278571</v>
+        <v>290.1981659616912</v>
       </c>
       <c r="D27" t="n">
-        <v>20.03413265278571</v>
+        <v>178.5185981156682</v>
       </c>
       <c r="E27" t="n">
-        <v>20.03413265278571</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="F27" t="n">
-        <v>20.03413265278571</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="G27" t="n">
-        <v>20.03413265278571</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="H27" t="n">
-        <v>20.03413265278571</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="I27" t="n">
-        <v>20.03413265278571</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J27" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K27" t="n">
-        <v>19.28</v>
+        <v>144.6387031680501</v>
       </c>
       <c r="L27" t="n">
-        <v>65.58652238664914</v>
+        <v>374.6018090363993</v>
       </c>
       <c r="M27" t="n">
-        <v>304.1765223866491</v>
+        <v>613.2059550252818</v>
       </c>
       <c r="N27" t="n">
-        <v>542.7665223866492</v>
+        <v>851.8101010141643</v>
       </c>
       <c r="O27" t="n">
-        <v>781.3565223866492</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="P27" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Q27" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="R27" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="S27" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="T27" t="n">
-        <v>761.813405358766</v>
+        <v>761.8705608694022</v>
       </c>
       <c r="U27" t="n">
-        <v>679.0802750576159</v>
+        <v>533.6469426057913</v>
       </c>
       <c r="V27" t="n">
-        <v>679.0802750576159</v>
+        <v>533.6469426057913</v>
       </c>
       <c r="W27" t="n">
-        <v>435.6459316232725</v>
+        <v>290.1981659616912</v>
       </c>
       <c r="X27" t="n">
-        <v>227.7944314177396</v>
+        <v>290.1981659616912</v>
       </c>
       <c r="Y27" t="n">
-        <v>20.03413265278571</v>
+        <v>290.1981659616912</v>
       </c>
     </row>
     <row r="28">
@@ -6343,76 +6343,76 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>19.28</v>
+        <v>829.5248650203655</v>
       </c>
       <c r="C28" t="n">
-        <v>19.28</v>
+        <v>829.5248650203655</v>
       </c>
       <c r="D28" t="n">
-        <v>19.28</v>
+        <v>829.5248650203655</v>
       </c>
       <c r="E28" t="n">
-        <v>19.28</v>
+        <v>829.5248650203655</v>
       </c>
       <c r="F28" t="n">
-        <v>19.28</v>
+        <v>829.5248650203655</v>
       </c>
       <c r="G28" t="n">
-        <v>19.28</v>
+        <v>829.5248650203655</v>
       </c>
       <c r="H28" t="n">
-        <v>19.28</v>
+        <v>829.5248650203655</v>
       </c>
       <c r="I28" t="n">
-        <v>19.28</v>
+        <v>829.5248650203655</v>
       </c>
       <c r="J28" t="n">
-        <v>19.28</v>
+        <v>829.5248650203655</v>
       </c>
       <c r="K28" t="n">
-        <v>19.28</v>
+        <v>829.5248650203655</v>
       </c>
       <c r="L28" t="n">
-        <v>46.59412500771298</v>
+        <v>856.8389900280785</v>
       </c>
       <c r="M28" t="n">
-        <v>85.78216319993516</v>
+        <v>896.0270282203006</v>
       </c>
       <c r="N28" t="n">
-        <v>129.4730138553714</v>
+        <v>939.7178788757369</v>
       </c>
       <c r="O28" t="n">
-        <v>153.8122904902707</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="P28" t="n">
-        <v>153.8122904902707</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Q28" t="n">
-        <v>153.8122904902707</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="R28" t="n">
-        <v>153.8122904902707</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="S28" t="n">
-        <v>153.8122904902707</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="T28" t="n">
-        <v>153.8122904902707</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="U28" t="n">
-        <v>153.8122904902707</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="V28" t="n">
-        <v>153.8122904902707</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="W28" t="n">
-        <v>19.28</v>
+        <v>829.5248650203655</v>
       </c>
       <c r="X28" t="n">
-        <v>19.28</v>
+        <v>829.5248650203655</v>
       </c>
       <c r="Y28" t="n">
-        <v>19.28</v>
+        <v>829.5248650203655</v>
       </c>
     </row>
     <row r="29">
@@ -6422,76 +6422,76 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>506.1486868686869</v>
+        <v>506.1786963984129</v>
       </c>
       <c r="C29" t="n">
-        <v>506.1486868686869</v>
+        <v>262.7299197543128</v>
       </c>
       <c r="D29" t="n">
-        <v>506.1486868686869</v>
+        <v>262.7299197543128</v>
       </c>
       <c r="E29" t="n">
-        <v>506.1486868686869</v>
+        <v>262.7299197543128</v>
       </c>
       <c r="F29" t="n">
-        <v>262.7143434343434</v>
+        <v>262.7299197543128</v>
       </c>
       <c r="G29" t="n">
-        <v>19.28</v>
+        <v>262.7299197543128</v>
       </c>
       <c r="H29" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="I29" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J29" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K29" t="n">
-        <v>122.2950059109224</v>
+        <v>122.2961490211351</v>
       </c>
       <c r="L29" t="n">
-        <v>302.3708574955809</v>
+        <v>302.3720006057937</v>
       </c>
       <c r="M29" t="n">
-        <v>519.3464847584851</v>
+        <v>519.3476278686978</v>
       </c>
       <c r="N29" t="n">
-        <v>725.2010069657244</v>
+        <v>725.2021500759372</v>
       </c>
       <c r="O29" t="n">
-        <v>874.3959571083725</v>
+        <v>874.3971002185853</v>
       </c>
       <c r="P29" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Q29" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="R29" t="n">
-        <v>964</v>
+        <v>812.6742080953335</v>
       </c>
       <c r="S29" t="n">
-        <v>964</v>
+        <v>749.627473042513</v>
       </c>
       <c r="T29" t="n">
-        <v>964</v>
+        <v>749.627473042513</v>
       </c>
       <c r="U29" t="n">
-        <v>964</v>
+        <v>749.627473042513</v>
       </c>
       <c r="V29" t="n">
-        <v>964</v>
+        <v>749.627473042513</v>
       </c>
       <c r="W29" t="n">
-        <v>964</v>
+        <v>749.627473042513</v>
       </c>
       <c r="X29" t="n">
-        <v>964</v>
+        <v>506.1786963984129</v>
       </c>
       <c r="Y29" t="n">
-        <v>720.5656565656566</v>
+        <v>506.1786963984129</v>
       </c>
     </row>
     <row r="30">
@@ -6501,76 +6501,76 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>55.00333542906893</v>
+        <v>485.4562706347935</v>
       </c>
       <c r="C30" t="n">
-        <v>55.00333542906893</v>
+        <v>311.0032413536665</v>
       </c>
       <c r="D30" t="n">
-        <v>55.00333542906893</v>
+        <v>311.0032413536665</v>
       </c>
       <c r="E30" t="n">
-        <v>19.28</v>
+        <v>311.0032413536665</v>
       </c>
       <c r="F30" t="n">
-        <v>19.28</v>
+        <v>311.0032413536665</v>
       </c>
       <c r="G30" t="n">
-        <v>19.28</v>
+        <v>172.272415936282</v>
       </c>
       <c r="H30" t="n">
-        <v>19.28</v>
+        <v>58.90328034386128</v>
       </c>
       <c r="I30" t="n">
-        <v>19.28</v>
+        <v>20.03527576299844</v>
       </c>
       <c r="J30" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K30" t="n">
-        <v>19.28</v>
+        <v>144.6387031680501</v>
       </c>
       <c r="L30" t="n">
-        <v>19.28</v>
+        <v>374.6018090363993</v>
       </c>
       <c r="M30" t="n">
-        <v>234.7819638733197</v>
+        <v>613.2059550252818</v>
       </c>
       <c r="N30" t="n">
-        <v>473.3719638733197</v>
+        <v>851.8101010141643</v>
       </c>
       <c r="O30" t="n">
-        <v>711.9619638733197</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="P30" t="n">
-        <v>894.6054414866707</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Q30" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="R30" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="S30" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="T30" t="n">
-        <v>761.813405358766</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="U30" t="n">
-        <v>533.5897870951551</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="V30" t="n">
-        <v>298.4376788634124</v>
+        <v>728.9050472788936</v>
       </c>
       <c r="W30" t="n">
-        <v>55.00333542906893</v>
+        <v>485.4562706347935</v>
       </c>
       <c r="X30" t="n">
-        <v>55.00333542906893</v>
+        <v>485.4562706347935</v>
       </c>
       <c r="Y30" t="n">
-        <v>55.00333542906893</v>
+        <v>485.4562706347935</v>
       </c>
     </row>
     <row r="31">
@@ -6580,76 +6580,76 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="C31" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="D31" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="E31" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="F31" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="G31" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="H31" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="I31" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J31" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K31" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="L31" t="n">
-        <v>46.59412500771298</v>
+        <v>46.5952681179257</v>
       </c>
       <c r="M31" t="n">
-        <v>85.78216319993516</v>
+        <v>85.78330631014788</v>
       </c>
       <c r="N31" t="n">
-        <v>129.4730138553714</v>
+        <v>129.4741569655842</v>
       </c>
       <c r="O31" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="P31" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="Q31" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="R31" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="S31" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="T31" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="U31" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="V31" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="W31" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="X31" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="Y31" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
     </row>
     <row r="32">
@@ -6659,76 +6659,76 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>234.3717171717172</v>
+        <v>234.8012144439637</v>
       </c>
       <c r="C32" t="n">
-        <v>234.3717171717172</v>
+        <v>234.8012144439637</v>
       </c>
       <c r="D32" t="n">
-        <v>234.3717171717172</v>
+        <v>234.8012144439637</v>
       </c>
       <c r="E32" t="n">
-        <v>234.3717171717172</v>
+        <v>234.8012144439637</v>
       </c>
       <c r="F32" t="n">
-        <v>234.3717171717172</v>
+        <v>234.8012144439637</v>
       </c>
       <c r="G32" t="n">
-        <v>234.3717171717172</v>
+        <v>234.8012144439637</v>
       </c>
       <c r="H32" t="n">
-        <v>17.2</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="I32" t="n">
-        <v>17.2</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="J32" t="n">
-        <v>17.2</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="K32" t="n">
-        <v>22.36462077340309</v>
+        <v>120.2465257255646</v>
       </c>
       <c r="L32" t="n">
-        <v>202.4404723580617</v>
+        <v>300.3223773102232</v>
       </c>
       <c r="M32" t="n">
-        <v>415.2904723580617</v>
+        <v>416.8664630901746</v>
       </c>
       <c r="N32" t="n">
-        <v>621.144994565301</v>
+        <v>622.7209852974139</v>
       </c>
       <c r="O32" t="n">
-        <v>770.339944707949</v>
+        <v>771.915935440062</v>
       </c>
       <c r="P32" t="n">
-        <v>860</v>
+        <v>861.5759907321129</v>
       </c>
       <c r="Q32" t="n">
-        <v>860</v>
+        <v>851.4843753638859</v>
       </c>
       <c r="R32" t="n">
-        <v>860</v>
+        <v>700.1014279485831</v>
       </c>
       <c r="S32" t="n">
-        <v>860</v>
+        <v>669.9406037026066</v>
       </c>
       <c r="T32" t="n">
-        <v>860</v>
+        <v>452.3709090732851</v>
       </c>
       <c r="U32" t="n">
-        <v>642.8282828282828</v>
+        <v>234.8012144439637</v>
       </c>
       <c r="V32" t="n">
-        <v>451.5434343434343</v>
+        <v>234.8012144439637</v>
       </c>
       <c r="W32" t="n">
-        <v>451.5434343434343</v>
+        <v>234.8012144439637</v>
       </c>
       <c r="X32" t="n">
-        <v>234.3717171717172</v>
+        <v>234.8012144439637</v>
       </c>
       <c r="Y32" t="n">
-        <v>234.3717171717172</v>
+        <v>234.8012144439637</v>
       </c>
     </row>
     <row r="33">
@@ -6738,76 +6738,76 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>367.4033227083792</v>
+        <v>325.2670720263557</v>
       </c>
       <c r="C33" t="n">
-        <v>367.4033227083792</v>
+        <v>150.8140427452286</v>
       </c>
       <c r="D33" t="n">
-        <v>367.4033227083792</v>
+        <v>150.8140427452286</v>
       </c>
       <c r="E33" t="n">
-        <v>367.4033227083792</v>
+        <v>150.8140427452286</v>
       </c>
       <c r="F33" t="n">
-        <v>220.8687647352642</v>
+        <v>150.8140427452286</v>
       </c>
       <c r="G33" t="n">
-        <v>220.8687647352642</v>
+        <v>17.98565246742797</v>
       </c>
       <c r="H33" t="n">
-        <v>107.4996291428435</v>
+        <v>17.98565246742797</v>
       </c>
       <c r="I33" t="n">
-        <v>17.2</v>
+        <v>17.98565246742797</v>
       </c>
       <c r="J33" t="n">
-        <v>17.2</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="K33" t="n">
-        <v>142.5575600578374</v>
+        <v>142.5890798724797</v>
       </c>
       <c r="L33" t="n">
-        <v>355.4075600578374</v>
+        <v>355.8291375786776</v>
       </c>
       <c r="M33" t="n">
-        <v>568.2575600578374</v>
+        <v>465.6924554125641</v>
       </c>
       <c r="N33" t="n">
-        <v>577.7554414866706</v>
+        <v>465.6924554125641</v>
       </c>
       <c r="O33" t="n">
-        <v>790.6054414866707</v>
+        <v>678.932513118762</v>
       </c>
       <c r="P33" t="n">
-        <v>790.6054414866707</v>
+        <v>861.5759907321129</v>
       </c>
       <c r="Q33" t="n">
-        <v>860</v>
+        <v>861.5759907321129</v>
       </c>
       <c r="R33" t="n">
-        <v>860</v>
+        <v>760.4064612849986</v>
       </c>
       <c r="S33" t="n">
-        <v>686.5826554506689</v>
+        <v>760.4064612849986</v>
       </c>
       <c r="T33" t="n">
-        <v>686.5826554506689</v>
+        <v>760.4064612849986</v>
       </c>
       <c r="U33" t="n">
-        <v>686.5826554506689</v>
+        <v>542.8367666556771</v>
       </c>
       <c r="V33" t="n">
-        <v>686.5826554506689</v>
+        <v>542.8367666556771</v>
       </c>
       <c r="W33" t="n">
-        <v>686.5826554506689</v>
+        <v>325.2670720263557</v>
       </c>
       <c r="X33" t="n">
-        <v>686.5826554506689</v>
+        <v>325.2670720263557</v>
       </c>
       <c r="Y33" t="n">
-        <v>478.822356685715</v>
+        <v>325.2670720263557</v>
       </c>
     </row>
     <row r="34">
@@ -6817,76 +6817,76 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>860</v>
+        <v>727.0437002418422</v>
       </c>
       <c r="C34" t="n">
-        <v>860</v>
+        <v>727.0437002418422</v>
       </c>
       <c r="D34" t="n">
-        <v>860</v>
+        <v>727.0437002418422</v>
       </c>
       <c r="E34" t="n">
-        <v>860</v>
+        <v>727.0437002418422</v>
       </c>
       <c r="F34" t="n">
-        <v>860</v>
+        <v>727.0437002418422</v>
       </c>
       <c r="G34" t="n">
-        <v>860</v>
+        <v>727.0437002418422</v>
       </c>
       <c r="H34" t="n">
-        <v>819.7699116477826</v>
+        <v>727.0437002418422</v>
       </c>
       <c r="I34" t="n">
-        <v>819.7699116477826</v>
+        <v>727.0437002418422</v>
       </c>
       <c r="J34" t="n">
-        <v>725.4677095097293</v>
+        <v>727.0437002418422</v>
       </c>
       <c r="K34" t="n">
-        <v>725.4677095097293</v>
+        <v>727.0437002418422</v>
       </c>
       <c r="L34" t="n">
-        <v>752.7818345174422</v>
+        <v>754.3578252495552</v>
       </c>
       <c r="M34" t="n">
-        <v>791.9698727096644</v>
+        <v>793.5458634417773</v>
       </c>
       <c r="N34" t="n">
-        <v>835.6607233651007</v>
+        <v>837.2367140972136</v>
       </c>
       <c r="O34" t="n">
-        <v>860</v>
+        <v>861.5759907321129</v>
       </c>
       <c r="P34" t="n">
-        <v>860</v>
+        <v>861.5759907321129</v>
       </c>
       <c r="Q34" t="n">
-        <v>860</v>
+        <v>861.5759907321129</v>
       </c>
       <c r="R34" t="n">
-        <v>860</v>
+        <v>861.5759907321129</v>
       </c>
       <c r="S34" t="n">
-        <v>860</v>
+        <v>861.5759907321129</v>
       </c>
       <c r="T34" t="n">
-        <v>860</v>
+        <v>861.5759907321129</v>
       </c>
       <c r="U34" t="n">
-        <v>860</v>
+        <v>861.5759907321129</v>
       </c>
       <c r="V34" t="n">
-        <v>860</v>
+        <v>861.5759907321129</v>
       </c>
       <c r="W34" t="n">
-        <v>860</v>
+        <v>861.5759907321129</v>
       </c>
       <c r="X34" t="n">
-        <v>860</v>
+        <v>861.5759907321129</v>
       </c>
       <c r="Y34" t="n">
-        <v>860</v>
+        <v>727.0437002418422</v>
       </c>
     </row>
     <row r="35">
@@ -6896,76 +6896,76 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>668.7151515151515</v>
+        <v>416.3449861052429</v>
       </c>
       <c r="C35" t="n">
-        <v>451.5434343434343</v>
+        <v>198.7752914759215</v>
       </c>
       <c r="D35" t="n">
-        <v>451.5434343434343</v>
+        <v>198.7752914759215</v>
       </c>
       <c r="E35" t="n">
-        <v>234.3717171717172</v>
+        <v>198.7752914759215</v>
       </c>
       <c r="F35" t="n">
-        <v>234.3717171717172</v>
+        <v>198.7752914759215</v>
       </c>
       <c r="G35" t="n">
-        <v>234.3717171717172</v>
+        <v>198.7752914759215</v>
       </c>
       <c r="H35" t="n">
-        <v>17.2</v>
+        <v>198.7752914759215</v>
       </c>
       <c r="I35" t="n">
-        <v>17.2</v>
+        <v>29.30150906172561</v>
       </c>
       <c r="J35" t="n">
-        <v>17.2</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="K35" t="n">
-        <v>120.2150059109224</v>
+        <v>120.2465257255646</v>
       </c>
       <c r="L35" t="n">
-        <v>300.290857495581</v>
+        <v>300.3223773102232</v>
       </c>
       <c r="M35" t="n">
-        <v>415.2904723580617</v>
+        <v>513.5624350164212</v>
       </c>
       <c r="N35" t="n">
-        <v>621.144994565301</v>
+        <v>622.7209852974139</v>
       </c>
       <c r="O35" t="n">
-        <v>770.339944707949</v>
+        <v>771.915935440062</v>
       </c>
       <c r="P35" t="n">
-        <v>860</v>
+        <v>861.5759907321129</v>
       </c>
       <c r="Q35" t="n">
-        <v>860</v>
+        <v>851.4843753638859</v>
       </c>
       <c r="R35" t="n">
-        <v>860</v>
+        <v>851.4843753638859</v>
       </c>
       <c r="S35" t="n">
-        <v>860</v>
+        <v>851.4843753638859</v>
       </c>
       <c r="T35" t="n">
-        <v>860</v>
+        <v>851.4843753638859</v>
       </c>
       <c r="U35" t="n">
-        <v>860</v>
+        <v>633.9146807345644</v>
       </c>
       <c r="V35" t="n">
-        <v>860</v>
+        <v>416.3449861052429</v>
       </c>
       <c r="W35" t="n">
-        <v>860</v>
+        <v>416.3449861052429</v>
       </c>
       <c r="X35" t="n">
-        <v>860</v>
+        <v>416.3449861052429</v>
       </c>
       <c r="Y35" t="n">
-        <v>860</v>
+        <v>416.3449861052429</v>
       </c>
     </row>
     <row r="36">
@@ -6975,76 +6975,76 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>17.95413265278571</v>
+        <v>464.1342098987335</v>
       </c>
       <c r="C36" t="n">
-        <v>17.95413265278571</v>
+        <v>464.1342098987335</v>
       </c>
       <c r="D36" t="n">
-        <v>17.95413265278571</v>
+        <v>315.1998002374822</v>
       </c>
       <c r="E36" t="n">
-        <v>17.95413265278571</v>
+        <v>155.9623452320268</v>
       </c>
       <c r="F36" t="n">
-        <v>17.95413265278571</v>
+        <v>155.9623452320268</v>
       </c>
       <c r="G36" t="n">
-        <v>17.95413265278571</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="H36" t="n">
-        <v>17.95413265278571</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="I36" t="n">
-        <v>17.95413265278571</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="J36" t="n">
-        <v>17.2</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="K36" t="n">
-        <v>17.2</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="L36" t="n">
-        <v>230.05</v>
+        <v>230.4715775208402</v>
       </c>
       <c r="M36" t="n">
-        <v>230.05</v>
+        <v>443.7116352270382</v>
       </c>
       <c r="N36" t="n">
-        <v>442.9</v>
+        <v>578.9413745125856</v>
       </c>
       <c r="O36" t="n">
-        <v>655.75</v>
+        <v>792.1814322187836</v>
       </c>
       <c r="P36" t="n">
-        <v>838.3934776133508</v>
+        <v>792.1814322187836</v>
       </c>
       <c r="Q36" t="n">
-        <v>860</v>
+        <v>861.5759907321129</v>
       </c>
       <c r="R36" t="n">
-        <v>860</v>
+        <v>861.5759907321129</v>
       </c>
       <c r="S36" t="n">
-        <v>860</v>
+        <v>861.5759907321129</v>
       </c>
       <c r="T36" t="n">
-        <v>669.4692841679373</v>
+        <v>861.5759907321129</v>
       </c>
       <c r="U36" t="n">
-        <v>452.2975669962201</v>
+        <v>861.5759907321129</v>
       </c>
       <c r="V36" t="n">
-        <v>235.1258498245029</v>
+        <v>861.5759907321129</v>
       </c>
       <c r="W36" t="n">
-        <v>17.95413265278571</v>
+        <v>644.0062961027915</v>
       </c>
       <c r="X36" t="n">
-        <v>17.95413265278571</v>
+        <v>644.0062961027915</v>
       </c>
       <c r="Y36" t="n">
-        <v>17.95413265278571</v>
+        <v>464.1342098987335</v>
       </c>
     </row>
     <row r="37">
@@ -7054,76 +7054,76 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>17.2</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="C37" t="n">
-        <v>17.2</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="D37" t="n">
-        <v>17.2</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="E37" t="n">
-        <v>17.2</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="F37" t="n">
-        <v>17.2</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="G37" t="n">
-        <v>17.2</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="H37" t="n">
-        <v>17.2</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="I37" t="n">
-        <v>17.2</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="J37" t="n">
-        <v>17.2</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="K37" t="n">
-        <v>17.2</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="L37" t="n">
-        <v>44.51412500771298</v>
+        <v>44.54564482235524</v>
       </c>
       <c r="M37" t="n">
-        <v>83.70216319993516</v>
+        <v>83.73368301457742</v>
       </c>
       <c r="N37" t="n">
-        <v>127.3930138553715</v>
+        <v>127.4245336700137</v>
       </c>
       <c r="O37" t="n">
-        <v>151.7322904902707</v>
+        <v>151.763810304913</v>
       </c>
       <c r="P37" t="n">
-        <v>148.9833604548096</v>
+        <v>151.763810304913</v>
       </c>
       <c r="Q37" t="n">
-        <v>61.9509935339062</v>
+        <v>151.763810304913</v>
       </c>
       <c r="R37" t="n">
-        <v>17.2</v>
+        <v>151.763810304913</v>
       </c>
       <c r="S37" t="n">
-        <v>17.2</v>
+        <v>151.763810304913</v>
       </c>
       <c r="T37" t="n">
-        <v>17.2</v>
+        <v>151.763810304913</v>
       </c>
       <c r="U37" t="n">
-        <v>17.2</v>
+        <v>151.763810304913</v>
       </c>
       <c r="V37" t="n">
-        <v>17.2</v>
+        <v>151.763810304913</v>
       </c>
       <c r="W37" t="n">
-        <v>17.2</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="X37" t="n">
-        <v>17.2</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="Y37" t="n">
-        <v>17.2</v>
+        <v>17.23151981464226</v>
       </c>
     </row>
     <row r="38">
@@ -7133,76 +7133,76 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>425.6565656565656</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="C38" t="n">
-        <v>234.3717171717172</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="D38" t="n">
-        <v>234.3717171717172</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="E38" t="n">
-        <v>234.3717171717172</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="F38" t="n">
-        <v>234.3717171717172</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="G38" t="n">
-        <v>17.2</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="H38" t="n">
-        <v>17.2</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="I38" t="n">
-        <v>17.2</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="J38" t="n">
-        <v>17.2</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="K38" t="n">
-        <v>120.2150059109224</v>
+        <v>120.2465257255646</v>
       </c>
       <c r="L38" t="n">
-        <v>300.290857495581</v>
+        <v>300.3223773102232</v>
       </c>
       <c r="M38" t="n">
-        <v>415.2904723580617</v>
+        <v>416.8664630901746</v>
       </c>
       <c r="N38" t="n">
-        <v>621.144994565301</v>
+        <v>622.7209852974139</v>
       </c>
       <c r="O38" t="n">
-        <v>770.339944707949</v>
+        <v>771.915935440062</v>
       </c>
       <c r="P38" t="n">
-        <v>860</v>
+        <v>861.5759907321129</v>
       </c>
       <c r="Q38" t="n">
-        <v>860</v>
+        <v>861.5759907321129</v>
       </c>
       <c r="R38" t="n">
-        <v>860</v>
+        <v>710.1930433168102</v>
       </c>
       <c r="S38" t="n">
-        <v>860</v>
+        <v>499.0616598963603</v>
       </c>
       <c r="T38" t="n">
-        <v>860</v>
+        <v>499.0616598963603</v>
       </c>
       <c r="U38" t="n">
-        <v>860</v>
+        <v>281.4919652670388</v>
       </c>
       <c r="V38" t="n">
-        <v>860</v>
+        <v>63.92227063771739</v>
       </c>
       <c r="W38" t="n">
-        <v>860</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="X38" t="n">
-        <v>860</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="Y38" t="n">
-        <v>642.8282828282828</v>
+        <v>17.23151981464226</v>
       </c>
     </row>
     <row r="39">
@@ -7212,76 +7212,76 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>166.1344096612513</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="C39" t="n">
-        <v>166.1344096612513</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="D39" t="n">
-        <v>17.2</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="E39" t="n">
-        <v>17.2</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="F39" t="n">
-        <v>17.2</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="G39" t="n">
-        <v>17.2</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="H39" t="n">
-        <v>17.2</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="I39" t="n">
-        <v>17.2</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="J39" t="n">
-        <v>17.2</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="K39" t="n">
-        <v>17.2</v>
+        <v>142.5890798724797</v>
       </c>
       <c r="L39" t="n">
-        <v>230.05</v>
+        <v>355.8291375786776</v>
       </c>
       <c r="M39" t="n">
-        <v>442.9</v>
+        <v>355.8291375786776</v>
       </c>
       <c r="N39" t="n">
-        <v>647.15</v>
+        <v>396.2978968992348</v>
       </c>
       <c r="O39" t="n">
-        <v>860</v>
+        <v>609.5379546054328</v>
       </c>
       <c r="P39" t="n">
-        <v>860</v>
+        <v>792.1814322187836</v>
       </c>
       <c r="Q39" t="n">
-        <v>860</v>
+        <v>861.5759907321129</v>
       </c>
       <c r="R39" t="n">
-        <v>860</v>
+        <v>861.5759907321129</v>
       </c>
       <c r="S39" t="n">
-        <v>860</v>
+        <v>861.5759907321129</v>
       </c>
       <c r="T39" t="n">
-        <v>657.813405358766</v>
+        <v>861.5759907321129</v>
       </c>
       <c r="U39" t="n">
-        <v>657.813405358766</v>
+        <v>644.0062961027915</v>
       </c>
       <c r="V39" t="n">
-        <v>440.6416881870488</v>
+        <v>426.43660147347</v>
       </c>
       <c r="W39" t="n">
-        <v>440.6416881870488</v>
+        <v>426.43660147347</v>
       </c>
       <c r="X39" t="n">
-        <v>373.8947084262052</v>
+        <v>218.5851012679371</v>
       </c>
       <c r="Y39" t="n">
-        <v>166.1344096612513</v>
+        <v>17.23151981464226</v>
       </c>
     </row>
     <row r="40">
@@ -7291,76 +7291,76 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>17.2</v>
+        <v>727.0437002418422</v>
       </c>
       <c r="C40" t="n">
-        <v>17.2</v>
+        <v>727.0437002418422</v>
       </c>
       <c r="D40" t="n">
-        <v>17.2</v>
+        <v>727.0437002418422</v>
       </c>
       <c r="E40" t="n">
-        <v>17.2</v>
+        <v>727.0437002418422</v>
       </c>
       <c r="F40" t="n">
-        <v>17.2</v>
+        <v>727.0437002418422</v>
       </c>
       <c r="G40" t="n">
-        <v>17.2</v>
+        <v>727.0437002418422</v>
       </c>
       <c r="H40" t="n">
-        <v>17.2</v>
+        <v>727.0437002418422</v>
       </c>
       <c r="I40" t="n">
-        <v>17.2</v>
+        <v>727.0437002418422</v>
       </c>
       <c r="J40" t="n">
-        <v>17.2</v>
+        <v>727.0437002418422</v>
       </c>
       <c r="K40" t="n">
-        <v>17.2</v>
+        <v>727.0437002418422</v>
       </c>
       <c r="L40" t="n">
-        <v>44.51412500771298</v>
+        <v>754.3578252495552</v>
       </c>
       <c r="M40" t="n">
-        <v>83.70216319993516</v>
+        <v>793.5458634417773</v>
       </c>
       <c r="N40" t="n">
-        <v>127.3930138553715</v>
+        <v>837.2367140972136</v>
       </c>
       <c r="O40" t="n">
-        <v>151.7322904902707</v>
+        <v>861.5759907321129</v>
       </c>
       <c r="P40" t="n">
-        <v>148.9833604548096</v>
+        <v>861.5759907321129</v>
       </c>
       <c r="Q40" t="n">
-        <v>61.9509935339062</v>
+        <v>861.5759907321129</v>
       </c>
       <c r="R40" t="n">
-        <v>17.2</v>
+        <v>861.5759907321129</v>
       </c>
       <c r="S40" t="n">
-        <v>17.2</v>
+        <v>861.5759907321129</v>
       </c>
       <c r="T40" t="n">
-        <v>17.2</v>
+        <v>861.5759907321129</v>
       </c>
       <c r="U40" t="n">
-        <v>17.2</v>
+        <v>727.0437002418422</v>
       </c>
       <c r="V40" t="n">
-        <v>17.2</v>
+        <v>727.0437002418422</v>
       </c>
       <c r="W40" t="n">
-        <v>17.2</v>
+        <v>727.0437002418422</v>
       </c>
       <c r="X40" t="n">
-        <v>17.2</v>
+        <v>727.0437002418422</v>
       </c>
       <c r="Y40" t="n">
-        <v>17.2</v>
+        <v>727.0437002418422</v>
       </c>
     </row>
     <row r="41">
@@ -7370,76 +7370,76 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>206.5454545454546</v>
+        <v>675.8841231162978</v>
       </c>
       <c r="C41" t="n">
-        <v>206.5454545454546</v>
+        <v>460.3040588563555</v>
       </c>
       <c r="D41" t="n">
-        <v>206.5454545454546</v>
+        <v>244.7239945964131</v>
       </c>
       <c r="E41" t="n">
-        <v>206.5454545454546</v>
+        <v>244.7239945964131</v>
       </c>
       <c r="F41" t="n">
-        <v>206.5454545454546</v>
+        <v>244.7239945964131</v>
       </c>
       <c r="G41" t="n">
-        <v>17.04</v>
+        <v>244.7239945964131</v>
       </c>
       <c r="H41" t="n">
-        <v>17.04</v>
+        <v>29.14393033647078</v>
       </c>
       <c r="I41" t="n">
-        <v>17.04</v>
+        <v>29.14393033647078</v>
       </c>
       <c r="J41" t="n">
-        <v>17.04</v>
+        <v>17.07394108938743</v>
       </c>
       <c r="K41" t="n">
-        <v>120.0550059109223</v>
+        <v>120.0889470003098</v>
       </c>
       <c r="L41" t="n">
-        <v>300.1308574955809</v>
+        <v>300.1647985849684</v>
       </c>
       <c r="M41" t="n">
-        <v>511.0008574955809</v>
+        <v>511.4548195661379</v>
       </c>
       <c r="N41" t="n">
-        <v>613.144994565301</v>
+        <v>717.3093417733771</v>
       </c>
       <c r="O41" t="n">
-        <v>762.339944707949</v>
+        <v>853.6970544693717</v>
       </c>
       <c r="P41" t="n">
-        <v>852</v>
+        <v>853.6970544693717</v>
       </c>
       <c r="Q41" t="n">
-        <v>852</v>
+        <v>843.6054391011446</v>
       </c>
       <c r="R41" t="n">
-        <v>852</v>
+        <v>843.6054391011446</v>
       </c>
       <c r="S41" t="n">
-        <v>852</v>
+        <v>843.6054391011446</v>
       </c>
       <c r="T41" t="n">
-        <v>852</v>
+        <v>843.6054391011446</v>
       </c>
       <c r="U41" t="n">
-        <v>852</v>
+        <v>675.8841231162978</v>
       </c>
       <c r="V41" t="n">
-        <v>852</v>
+        <v>675.8841231162978</v>
       </c>
       <c r="W41" t="n">
-        <v>636.8484848484849</v>
+        <v>675.8841231162978</v>
       </c>
       <c r="X41" t="n">
-        <v>421.6969696969697</v>
+        <v>675.8841231162978</v>
       </c>
       <c r="Y41" t="n">
-        <v>421.6969696969697</v>
+        <v>675.8841231162978</v>
       </c>
     </row>
     <row r="42">
@@ -7449,76 +7449,76 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>17.79413265278571</v>
+        <v>17.07394108938743</v>
       </c>
       <c r="C42" t="n">
-        <v>17.79413265278571</v>
+        <v>17.07394108938743</v>
       </c>
       <c r="D42" t="n">
-        <v>17.79413265278571</v>
+        <v>17.07394108938743</v>
       </c>
       <c r="E42" t="n">
-        <v>17.79413265278571</v>
+        <v>17.07394108938743</v>
       </c>
       <c r="F42" t="n">
-        <v>17.79413265278571</v>
+        <v>17.07394108938743</v>
       </c>
       <c r="G42" t="n">
-        <v>17.79413265278571</v>
+        <v>17.07394108938743</v>
       </c>
       <c r="H42" t="n">
-        <v>17.79413265278571</v>
+        <v>17.07394108938743</v>
       </c>
       <c r="I42" t="n">
-        <v>17.79413265278571</v>
+        <v>17.07394108938743</v>
       </c>
       <c r="J42" t="n">
-        <v>17.04</v>
+        <v>17.07394108938743</v>
       </c>
       <c r="K42" t="n">
-        <v>142.3975600578374</v>
+        <v>17.07394108938743</v>
       </c>
       <c r="L42" t="n">
-        <v>142.3975600578374</v>
+        <v>17.07394108938743</v>
       </c>
       <c r="M42" t="n">
-        <v>178.2219638733197</v>
+        <v>228.3639620705569</v>
       </c>
       <c r="N42" t="n">
-        <v>389.0919638733197</v>
+        <v>439.6539830517264</v>
       </c>
       <c r="O42" t="n">
-        <v>599.9619638733197</v>
+        <v>601.6590183426915</v>
       </c>
       <c r="P42" t="n">
-        <v>782.6054414866707</v>
+        <v>784.3024959560423</v>
       </c>
       <c r="Q42" t="n">
-        <v>852</v>
+        <v>853.6970544693717</v>
       </c>
       <c r="R42" t="n">
-        <v>852</v>
+        <v>853.6970544693717</v>
       </c>
       <c r="S42" t="n">
-        <v>852</v>
+        <v>853.6970544693717</v>
       </c>
       <c r="T42" t="n">
-        <v>852</v>
+        <v>853.6970544693717</v>
       </c>
       <c r="U42" t="n">
-        <v>636.8484848484849</v>
+        <v>638.1169902094293</v>
       </c>
       <c r="V42" t="n">
-        <v>421.6969696969697</v>
+        <v>422.536925949487</v>
       </c>
       <c r="W42" t="n">
-        <v>206.5454545454546</v>
+        <v>206.9568616895446</v>
       </c>
       <c r="X42" t="n">
-        <v>17.79413265278571</v>
+        <v>17.07394108938743</v>
       </c>
       <c r="Y42" t="n">
-        <v>17.79413265278571</v>
+        <v>17.07394108938743</v>
       </c>
     </row>
     <row r="43">
@@ -7528,76 +7528,76 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>852</v>
+        <v>719.1647639791009</v>
       </c>
       <c r="C43" t="n">
-        <v>852</v>
+        <v>719.1647639791009</v>
       </c>
       <c r="D43" t="n">
-        <v>717.4677095097293</v>
+        <v>719.1647639791009</v>
       </c>
       <c r="E43" t="n">
-        <v>717.4677095097293</v>
+        <v>719.1647639791009</v>
       </c>
       <c r="F43" t="n">
-        <v>717.4677095097293</v>
+        <v>719.1647639791009</v>
       </c>
       <c r="G43" t="n">
-        <v>717.4677095097293</v>
+        <v>719.1647639791009</v>
       </c>
       <c r="H43" t="n">
-        <v>717.4677095097293</v>
+        <v>719.1647639791009</v>
       </c>
       <c r="I43" t="n">
-        <v>717.4677095097293</v>
+        <v>719.1647639791009</v>
       </c>
       <c r="J43" t="n">
-        <v>717.4677095097293</v>
+        <v>719.1647639791009</v>
       </c>
       <c r="K43" t="n">
-        <v>717.4677095097293</v>
+        <v>719.1647639791009</v>
       </c>
       <c r="L43" t="n">
-        <v>744.7818345174422</v>
+        <v>746.4788889868139</v>
       </c>
       <c r="M43" t="n">
-        <v>783.9698727096644</v>
+        <v>785.6669271790361</v>
       </c>
       <c r="N43" t="n">
-        <v>827.6607233651007</v>
+        <v>829.3577778344724</v>
       </c>
       <c r="O43" t="n">
-        <v>852</v>
+        <v>853.6970544693717</v>
       </c>
       <c r="P43" t="n">
-        <v>852</v>
+        <v>853.6970544693717</v>
       </c>
       <c r="Q43" t="n">
-        <v>852</v>
+        <v>853.6970544693717</v>
       </c>
       <c r="R43" t="n">
-        <v>852</v>
+        <v>719.1647639791009</v>
       </c>
       <c r="S43" t="n">
-        <v>852</v>
+        <v>719.1647639791009</v>
       </c>
       <c r="T43" t="n">
-        <v>852</v>
+        <v>719.1647639791009</v>
       </c>
       <c r="U43" t="n">
-        <v>852</v>
+        <v>719.1647639791009</v>
       </c>
       <c r="V43" t="n">
-        <v>852</v>
+        <v>719.1647639791009</v>
       </c>
       <c r="W43" t="n">
-        <v>852</v>
+        <v>719.1647639791009</v>
       </c>
       <c r="X43" t="n">
-        <v>852</v>
+        <v>719.1647639791009</v>
       </c>
       <c r="Y43" t="n">
-        <v>852</v>
+        <v>719.1647639791009</v>
       </c>
     </row>
     <row r="44">
@@ -8433,13 +8433,13 @@
         <v>169.0966151720738</v>
       </c>
       <c r="K8" t="n">
-        <v>246.0898510449805</v>
+        <v>245.7101422396114</v>
       </c>
       <c r="L8" t="n">
-        <v>261.7664149699872</v>
+        <v>261.3867061646181</v>
       </c>
       <c r="M8" t="n">
-        <v>255.2957281767677</v>
+        <v>254.9313611413124</v>
       </c>
       <c r="N8" t="n">
         <v>229.4130635965909</v>
@@ -8448,7 +8448,7 @@
         <v>230.0982114216867</v>
       </c>
       <c r="P8" t="n">
-        <v>257.2329957552695</v>
+        <v>256.8532869499004</v>
       </c>
       <c r="Q8" t="n">
         <v>212.3149906599047</v>
@@ -8512,25 +8512,25 @@
         <v>126.0910353404088</v>
       </c>
       <c r="K9" t="n">
-        <v>162.790933923854</v>
+        <v>137.841438974359</v>
       </c>
       <c r="L9" t="n">
         <v>138.5543797798742</v>
       </c>
       <c r="M9" t="n">
-        <v>142.1340339220183</v>
+        <v>167.7543251166491</v>
       </c>
       <c r="N9" t="n">
-        <v>157.3417120833333</v>
+        <v>131.3417120833333</v>
       </c>
       <c r="O9" t="n">
-        <v>168.5962444444444</v>
+        <v>167.1813723584841</v>
       </c>
       <c r="P9" t="n">
-        <v>133.9744074143302</v>
+        <v>159.5946986089611</v>
       </c>
       <c r="Q9" t="n">
-        <v>165.9817740860215</v>
+        <v>165.6020652806523</v>
       </c>
       <c r="R9" t="n">
         <v>45.52166981132082</v>
@@ -8594,13 +8594,13 @@
         <v>106.7437663446525</v>
       </c>
       <c r="L10" t="n">
-        <v>160.8846762812383</v>
+        <v>160.5049674758691</v>
       </c>
       <c r="M10" t="n">
-        <v>164.9257839476051</v>
+        <v>164.5460751422359</v>
       </c>
       <c r="N10" t="n">
-        <v>153.6855444652332</v>
+        <v>153.305835659864</v>
       </c>
       <c r="O10" t="n">
         <v>163.0416663658825</v>
@@ -8670,22 +8670,22 @@
         <v>169.0966151720738</v>
       </c>
       <c r="K11" t="n">
-        <v>220.0898510449805</v>
+        <v>245.7101422396114</v>
       </c>
       <c r="L11" t="n">
-        <v>260.7159099194822</v>
+        <v>261.3867061646181</v>
       </c>
       <c r="M11" t="n">
         <v>230.3462332272727</v>
       </c>
       <c r="N11" t="n">
-        <v>255.4130635965909</v>
+        <v>229.4130635965909</v>
       </c>
       <c r="O11" t="n">
-        <v>256.0982114216868</v>
+        <v>254.6833393357264</v>
       </c>
       <c r="P11" t="n">
-        <v>257.2329957552695</v>
+        <v>256.8532869499004</v>
       </c>
       <c r="Q11" t="n">
         <v>212.3149906599047</v>
@@ -8752,22 +8752,22 @@
         <v>137.841438974359</v>
       </c>
       <c r="L12" t="n">
-        <v>164.5543797798742</v>
+        <v>164.174670974505</v>
       </c>
       <c r="M12" t="n">
-        <v>168.1340339220183</v>
+        <v>167.7543251166491</v>
       </c>
       <c r="N12" t="n">
-        <v>157.3417120833333</v>
+        <v>131.3417120833333</v>
       </c>
       <c r="O12" t="n">
-        <v>167.5457393939394</v>
+        <v>142.5962444444444</v>
       </c>
       <c r="P12" t="n">
-        <v>133.9744074143302</v>
+        <v>158.5595353283699</v>
       </c>
       <c r="Q12" t="n">
-        <v>139.9817740860215</v>
+        <v>165.6020652806523</v>
       </c>
       <c r="R12" t="n">
         <v>45.52166981132082</v>
@@ -8831,13 +8831,13 @@
         <v>106.7437663446525</v>
       </c>
       <c r="L13" t="n">
-        <v>160.8846762812383</v>
+        <v>160.5049674758691</v>
       </c>
       <c r="M13" t="n">
-        <v>164.9257839476051</v>
+        <v>164.5460751422359</v>
       </c>
       <c r="N13" t="n">
-        <v>153.6855444652332</v>
+        <v>153.305835659864</v>
       </c>
       <c r="O13" t="n">
         <v>163.0416663658825</v>
@@ -8907,22 +8907,22 @@
         <v>169.0966151720738</v>
       </c>
       <c r="K14" t="n">
-        <v>220.0898510449805</v>
+        <v>245.7101422396114</v>
       </c>
       <c r="L14" t="n">
-        <v>261.7664149699872</v>
+        <v>261.3867061646181</v>
       </c>
       <c r="M14" t="n">
-        <v>256.3462332272727</v>
+        <v>254.9313611413124</v>
       </c>
       <c r="N14" t="n">
-        <v>254.3625585460859</v>
+        <v>229.4130635965909</v>
       </c>
       <c r="O14" t="n">
-        <v>256.0982114216868</v>
+        <v>230.0982114216867</v>
       </c>
       <c r="P14" t="n">
-        <v>231.2329957552695</v>
+        <v>256.8532869499004</v>
       </c>
       <c r="Q14" t="n">
         <v>212.3149906599047</v>
@@ -8986,25 +8986,25 @@
         <v>126.0910353404088</v>
       </c>
       <c r="K15" t="n">
-        <v>162.790933923854</v>
+        <v>137.841438974359</v>
       </c>
       <c r="L15" t="n">
-        <v>138.5543797798742</v>
+        <v>164.174670974505</v>
       </c>
       <c r="M15" t="n">
-        <v>142.1340339220183</v>
+        <v>167.7543251166491</v>
       </c>
       <c r="N15" t="n">
-        <v>157.3417120833333</v>
+        <v>131.3417120833333</v>
       </c>
       <c r="O15" t="n">
-        <v>168.5962444444444</v>
+        <v>142.5962444444444</v>
       </c>
       <c r="P15" t="n">
-        <v>159.9744074143302</v>
+        <v>158.5595353283699</v>
       </c>
       <c r="Q15" t="n">
-        <v>139.9817740860215</v>
+        <v>165.6020652806523</v>
       </c>
       <c r="R15" t="n">
         <v>45.52166981132082</v>
@@ -9068,13 +9068,13 @@
         <v>106.7437663446525</v>
       </c>
       <c r="L16" t="n">
-        <v>160.8846762812383</v>
+        <v>160.5049674758691</v>
       </c>
       <c r="M16" t="n">
-        <v>164.9257839476051</v>
+        <v>164.5460751422359</v>
       </c>
       <c r="N16" t="n">
-        <v>153.6855444652332</v>
+        <v>153.305835659864</v>
       </c>
       <c r="O16" t="n">
         <v>163.0416663658825</v>
@@ -9144,22 +9144,22 @@
         <v>169.0966151720738</v>
       </c>
       <c r="K17" t="n">
-        <v>248.0898510449805</v>
+        <v>247.6798763052967</v>
       </c>
       <c r="L17" t="n">
-        <v>262.6351018386741</v>
+        <v>263.3564402303034</v>
       </c>
       <c r="M17" t="n">
-        <v>230.3462332272727</v>
+        <v>257.9362584875889</v>
       </c>
       <c r="N17" t="n">
-        <v>229.4130635965909</v>
+        <v>255.8883403615407</v>
       </c>
       <c r="O17" t="n">
-        <v>258.0982114216868</v>
+        <v>230.0982114216867</v>
       </c>
       <c r="P17" t="n">
-        <v>259.2329957552695</v>
+        <v>231.2329957552695</v>
       </c>
       <c r="Q17" t="n">
         <v>212.3149906599047</v>
@@ -9223,25 +9223,25 @@
         <v>126.0910353404088</v>
       </c>
       <c r="K18" t="n">
-        <v>165.841438974359</v>
+        <v>165.4314642346751</v>
       </c>
       <c r="L18" t="n">
-        <v>166.5543797798742</v>
+        <v>138.5543797798742</v>
       </c>
       <c r="M18" t="n">
-        <v>169.0027207907052</v>
+        <v>142.1340339220183</v>
       </c>
       <c r="N18" t="n">
-        <v>131.3417120833333</v>
+        <v>158.9317373436494</v>
       </c>
       <c r="O18" t="n">
-        <v>142.5962444444444</v>
+        <v>170.1862697047606</v>
       </c>
       <c r="P18" t="n">
-        <v>133.9744074143302</v>
+        <v>160.4496841792801</v>
       </c>
       <c r="Q18" t="n">
-        <v>167.9817740860215</v>
+        <v>139.9817740860215</v>
       </c>
       <c r="R18" t="n">
         <v>45.52166981132082</v>
@@ -9308,10 +9308,10 @@
         <v>162.4747015415544</v>
       </c>
       <c r="M19" t="n">
-        <v>166.9257839476051</v>
+        <v>166.5158092079212</v>
       </c>
       <c r="N19" t="n">
-        <v>155.6855444652332</v>
+        <v>155.2755697255493</v>
       </c>
       <c r="O19" t="n">
         <v>163.0416663658825</v>
@@ -9381,7 +9381,7 @@
         <v>169.0966151720738</v>
       </c>
       <c r="K20" t="n">
-        <v>324.0888343889188</v>
+        <v>324.1454125711647</v>
       </c>
       <c r="L20" t="n">
         <v>417.6612145504504</v>
@@ -9463,22 +9463,22 @@
         <v>137.841438974359</v>
       </c>
       <c r="L21" t="n">
-        <v>138.5543797798742</v>
+        <v>370.8403453034592</v>
       </c>
       <c r="M21" t="n">
-        <v>359.81278530921</v>
+        <v>383.1483227996774</v>
       </c>
       <c r="N21" t="n">
-        <v>372.3417120833333</v>
+        <v>371.3463732493024</v>
       </c>
       <c r="O21" t="n">
-        <v>383.5962444444444</v>
+        <v>383.6105333221035</v>
       </c>
       <c r="P21" t="n">
-        <v>318.4627686399372</v>
+        <v>133.9744074143302</v>
       </c>
       <c r="Q21" t="n">
-        <v>210.0772877358491</v>
+        <v>139.9817740860215</v>
       </c>
       <c r="R21" t="n">
         <v>45.52166981132082</v>
@@ -9618,7 +9618,7 @@
         <v>169.0966151720738</v>
       </c>
       <c r="K23" t="n">
-        <v>324.0888343889188</v>
+        <v>324.1454125711647</v>
       </c>
       <c r="L23" t="n">
         <v>417.6612145504504</v>
@@ -9697,25 +9697,25 @@
         <v>126.0910353404088</v>
       </c>
       <c r="K24" t="n">
-        <v>264.4652370125786</v>
+        <v>137.841438974359</v>
       </c>
       <c r="L24" t="n">
-        <v>370.8403453034592</v>
+        <v>138.5543797798742</v>
       </c>
       <c r="M24" t="n">
-        <v>383.1340339220183</v>
+        <v>359.8407857361378</v>
       </c>
       <c r="N24" t="n">
-        <v>372.3417120833333</v>
+        <v>372.3560009609923</v>
       </c>
       <c r="O24" t="n">
-        <v>255.9491071452661</v>
+        <v>383.6105333221035</v>
       </c>
       <c r="P24" t="n">
-        <v>133.9744074143302</v>
+        <v>318.4627686399372</v>
       </c>
       <c r="Q24" t="n">
-        <v>139.9817740860215</v>
+        <v>210.0772877358491</v>
       </c>
       <c r="R24" t="n">
         <v>45.52166981132082</v>
@@ -9855,7 +9855,7 @@
         <v>169.0966151720738</v>
       </c>
       <c r="K26" t="n">
-        <v>324.0888343889188</v>
+        <v>324.1454125711648</v>
       </c>
       <c r="L26" t="n">
         <v>417.6612145504504</v>
@@ -9934,22 +9934,22 @@
         <v>126.0910353404088</v>
       </c>
       <c r="K27" t="n">
-        <v>137.841438974359</v>
+        <v>264.4652370125786</v>
       </c>
       <c r="L27" t="n">
-        <v>185.3286448168935</v>
+        <v>370.8403453034592</v>
       </c>
       <c r="M27" t="n">
-        <v>383.1340339220183</v>
+        <v>383.1483227996774</v>
       </c>
       <c r="N27" t="n">
-        <v>372.3417120833333</v>
+        <v>372.3560009609923</v>
       </c>
       <c r="O27" t="n">
-        <v>383.5962444444444</v>
+        <v>255.9771075721939</v>
       </c>
       <c r="P27" t="n">
-        <v>318.4627686399372</v>
+        <v>133.9744074143302</v>
       </c>
       <c r="Q27" t="n">
         <v>139.9817740860215</v>
@@ -10107,7 +10107,7 @@
         <v>380.8001812627454</v>
       </c>
       <c r="P29" t="n">
-        <v>321.7421299892367</v>
+        <v>321.7987081714826</v>
       </c>
       <c r="Q29" t="n">
         <v>212.3149906599047</v>
@@ -10171,25 +10171,25 @@
         <v>126.0910353404088</v>
       </c>
       <c r="K30" t="n">
-        <v>137.841438974359</v>
+        <v>264.4652370125786</v>
       </c>
       <c r="L30" t="n">
-        <v>138.5543797798742</v>
+        <v>370.8403453034592</v>
       </c>
       <c r="M30" t="n">
-        <v>359.81278530921</v>
+        <v>383.1483227996774</v>
       </c>
       <c r="N30" t="n">
-        <v>372.3417120833333</v>
+        <v>372.3560009609923</v>
       </c>
       <c r="O30" t="n">
-        <v>383.5962444444444</v>
+        <v>255.9771075721939</v>
       </c>
       <c r="P30" t="n">
-        <v>318.4627686399372</v>
+        <v>133.9744074143302</v>
       </c>
       <c r="Q30" t="n">
-        <v>210.0772877358491</v>
+        <v>139.9817740860215</v>
       </c>
       <c r="R30" t="n">
         <v>45.52166981132082</v>
@@ -10329,13 +10329,13 @@
         <v>169.0966151720738</v>
       </c>
       <c r="K32" t="n">
-        <v>225.3066397049837</v>
+        <v>324.1454125711647</v>
       </c>
       <c r="L32" t="n">
         <v>417.6612145504504</v>
       </c>
       <c r="M32" t="n">
-        <v>445.3462332272727</v>
+        <v>348.0675319949004</v>
       </c>
       <c r="N32" t="n">
         <v>437.3469244119842</v>
@@ -10411,22 +10411,22 @@
         <v>264.4652370125786</v>
       </c>
       <c r="L33" t="n">
-        <v>353.5543797798742</v>
+        <v>353.9483774629024</v>
       </c>
       <c r="M33" t="n">
-        <v>357.1340339220183</v>
+        <v>253.1070822390753</v>
       </c>
       <c r="N33" t="n">
-        <v>140.9355317084174</v>
+        <v>131.3417120833333</v>
       </c>
       <c r="O33" t="n">
-        <v>357.5962444444444</v>
+        <v>357.9902421274727</v>
       </c>
       <c r="P33" t="n">
-        <v>133.9744074143302</v>
+        <v>318.4627686399372</v>
       </c>
       <c r="Q33" t="n">
-        <v>210.0772877358491</v>
+        <v>139.9817740860215</v>
       </c>
       <c r="R33" t="n">
         <v>45.52166981132082</v>
@@ -10572,10 +10572,10 @@
         <v>417.6612145504504</v>
       </c>
       <c r="M35" t="n">
-        <v>346.5074603610916</v>
+        <v>445.740230910301</v>
       </c>
       <c r="N35" t="n">
-        <v>437.3469244119842</v>
+        <v>339.6742254965835</v>
       </c>
       <c r="O35" t="n">
         <v>380.8001812627454</v>
@@ -10648,22 +10648,22 @@
         <v>137.841438974359</v>
       </c>
       <c r="L36" t="n">
-        <v>353.5543797798742</v>
+        <v>353.9483774629024</v>
       </c>
       <c r="M36" t="n">
-        <v>142.1340339220183</v>
+        <v>357.5280316050465</v>
       </c>
       <c r="N36" t="n">
-        <v>346.3417120833333</v>
+        <v>267.937408331361</v>
       </c>
       <c r="O36" t="n">
-        <v>357.5962444444444</v>
+        <v>357.9902421274727</v>
       </c>
       <c r="P36" t="n">
-        <v>318.4627686399372</v>
+        <v>133.9744074143302</v>
       </c>
       <c r="Q36" t="n">
-        <v>161.806544173546</v>
+        <v>210.0772877358491</v>
       </c>
       <c r="R36" t="n">
         <v>45.52166981132082</v>
@@ -10809,7 +10809,7 @@
         <v>417.6612145504504</v>
       </c>
       <c r="M38" t="n">
-        <v>346.5074603610916</v>
+        <v>348.0675319949004</v>
       </c>
       <c r="N38" t="n">
         <v>437.3469244119842</v>
@@ -10882,25 +10882,25 @@
         <v>126.0910353404088</v>
       </c>
       <c r="K39" t="n">
-        <v>137.841438974359</v>
+        <v>264.4652370125786</v>
       </c>
       <c r="L39" t="n">
-        <v>353.5543797798742</v>
+        <v>353.9483774629024</v>
       </c>
       <c r="M39" t="n">
-        <v>357.1340339220183</v>
+        <v>142.1340339220183</v>
       </c>
       <c r="N39" t="n">
-        <v>337.6548433964646</v>
+        <v>172.2192467505628</v>
       </c>
       <c r="O39" t="n">
-        <v>357.5962444444444</v>
+        <v>357.9902421274727</v>
       </c>
       <c r="P39" t="n">
-        <v>133.9744074143302</v>
+        <v>318.4627686399372</v>
       </c>
       <c r="Q39" t="n">
-        <v>139.9817740860215</v>
+        <v>210.0772877358491</v>
       </c>
       <c r="R39" t="n">
         <v>45.52166981132082</v>
@@ -11046,16 +11046,16 @@
         <v>417.6612145504504</v>
       </c>
       <c r="M41" t="n">
-        <v>443.3462332272727</v>
+        <v>443.7704968446156</v>
       </c>
       <c r="N41" t="n">
-        <v>332.5889596266112</v>
+        <v>437.3469244119842</v>
       </c>
       <c r="O41" t="n">
-        <v>380.8001812627454</v>
+        <v>367.8635777812772</v>
       </c>
       <c r="P41" t="n">
-        <v>321.7987081714826</v>
+        <v>231.2329957552695</v>
       </c>
       <c r="Q41" t="n">
         <v>212.3149906599047</v>
@@ -11119,19 +11119,19 @@
         <v>126.0910353404088</v>
       </c>
       <c r="K42" t="n">
-        <v>264.4652370125786</v>
+        <v>137.841438974359</v>
       </c>
       <c r="L42" t="n">
         <v>138.5543797798742</v>
       </c>
       <c r="M42" t="n">
-        <v>178.3203004023035</v>
+        <v>355.5582975393612</v>
       </c>
       <c r="N42" t="n">
-        <v>344.3417120833333</v>
+        <v>344.7659757006762</v>
       </c>
       <c r="O42" t="n">
-        <v>355.5962444444444</v>
+        <v>306.2376942332981</v>
       </c>
       <c r="P42" t="n">
         <v>318.4627686399372</v>
@@ -22978,10 +22978,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>356.7338416634806</v>
+        <v>382.7338416634806</v>
       </c>
       <c r="C8" t="n">
-        <v>352.3627909855524</v>
+        <v>365.2728917710076</v>
       </c>
       <c r="D8" t="n">
         <v>354.683041620683</v>
@@ -22990,7 +22990,7 @@
         <v>381.9303700722618</v>
       </c>
       <c r="F8" t="n">
-        <v>380.8760457417114</v>
+        <v>406.8760457417114</v>
       </c>
       <c r="G8" t="n">
         <v>415.302737515135</v>
@@ -23002,7 +23002,7 @@
         <v>210.4758895704059</v>
       </c>
       <c r="J8" t="n">
-        <v>11.94928935461252</v>
+        <v>0</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
@@ -23026,7 +23026,7 @@
         <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>123.8691179411497</v>
+        <v>124.2488267465189</v>
       </c>
       <c r="S8" t="n">
         <v>209.0200695862453</v>
@@ -23041,13 +23041,13 @@
         <v>327.7522584701349</v>
       </c>
       <c r="W8" t="n">
-        <v>349.240968717413</v>
+        <v>348.6146048023395</v>
       </c>
       <c r="X8" t="n">
-        <v>369.731100678469</v>
+        <v>344.1108094838382</v>
       </c>
       <c r="Y8" t="n">
-        <v>386.2379386560536</v>
+        <v>360.6176474614227</v>
       </c>
     </row>
     <row r="9">
@@ -23069,16 +23069,16 @@
         <v>157.6450804554009</v>
       </c>
       <c r="F9" t="n">
-        <v>122.9150037196417</v>
+        <v>123.2494512354109</v>
       </c>
       <c r="G9" t="n">
-        <v>111.3435171632106</v>
+        <v>111.7232259685798</v>
       </c>
       <c r="H9" t="n">
-        <v>86.23544423649646</v>
+        <v>86.61515304186563</v>
       </c>
       <c r="I9" t="n">
-        <v>63.39663285141508</v>
+        <v>63.77634165678425</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -23151,19 +23151,19 @@
         <v>145.4210480229312</v>
       </c>
       <c r="G10" t="n">
-        <v>167.7167873157914</v>
+        <v>167.9909793584588</v>
       </c>
       <c r="H10" t="n">
-        <v>136.2271725074396</v>
+        <v>162.2271725074396</v>
       </c>
       <c r="I10" t="n">
-        <v>129.4504749272583</v>
+        <v>155.4504749272583</v>
       </c>
       <c r="J10" t="n">
-        <v>67.35918011667277</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>22.26949182588285</v>
       </c>
       <c r="L10" t="n">
         <v>0</v>
@@ -23178,19 +23178,19 @@
         <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>2.721440735106512</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>86.16204325169439</v>
+        <v>60.54175205706355</v>
       </c>
       <c r="R10" t="n">
-        <v>177.2933913771695</v>
+        <v>151.6731001825387</v>
       </c>
       <c r="S10" t="n">
-        <v>224.0165980369723</v>
+        <v>198.3963068423414</v>
       </c>
       <c r="T10" t="n">
-        <v>227.9455894282815</v>
+        <v>208.1006776791572</v>
       </c>
       <c r="U10" t="n">
         <v>286.3190293564909</v>
@@ -23224,22 +23224,22 @@
         <v>354.683041620683</v>
       </c>
       <c r="E11" t="n">
-        <v>381.9303700722618</v>
+        <v>356.3100788776309</v>
       </c>
       <c r="F11" t="n">
-        <v>405.9152343108688</v>
+        <v>381.2557545470806</v>
       </c>
       <c r="G11" t="n">
-        <v>389.302737515135</v>
+        <v>389.6824463205042</v>
       </c>
       <c r="H11" t="n">
-        <v>313.4748021157671</v>
+        <v>316.9084496315363</v>
       </c>
       <c r="I11" t="n">
-        <v>184.4758895704059</v>
+        <v>210.4758895704059</v>
       </c>
       <c r="J11" t="n">
-        <v>0</v>
+        <v>11.94928935461252</v>
       </c>
       <c r="K11" t="n">
         <v>0</v>
@@ -23260,7 +23260,7 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>9.990699214544804</v>
       </c>
       <c r="R11" t="n">
         <v>149.8691179411497</v>
@@ -23306,16 +23306,16 @@
         <v>157.6450804554009</v>
       </c>
       <c r="F12" t="n">
-        <v>145.0692123933839</v>
+        <v>123.2494512354109</v>
       </c>
       <c r="G12" t="n">
-        <v>137.3435171632106</v>
+        <v>111.7232259685798</v>
       </c>
       <c r="H12" t="n">
-        <v>90.08123556275433</v>
+        <v>86.61515304186563</v>
       </c>
       <c r="I12" t="n">
-        <v>63.39663285141508</v>
+        <v>63.77634165678425</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -23342,10 +23342,10 @@
         <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>74.15783415264313</v>
+        <v>100.1578341526431</v>
       </c>
       <c r="S12" t="n">
-        <v>145.6831711038378</v>
+        <v>171.6831711038378</v>
       </c>
       <c r="T12" t="n">
         <v>200.1647286948216</v>
@@ -23418,16 +23418,16 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>60.16204325169439</v>
+        <v>60.54175205706355</v>
       </c>
       <c r="R13" t="n">
-        <v>151.2933913771695</v>
+        <v>151.6731001825387</v>
       </c>
       <c r="S13" t="n">
-        <v>198.0165980369723</v>
+        <v>198.3963068423414</v>
       </c>
       <c r="T13" t="n">
-        <v>208.1233462948377</v>
+        <v>208.1006776791572</v>
       </c>
       <c r="U13" t="n">
         <v>286.3190293564909</v>
@@ -23464,19 +23464,19 @@
         <v>381.9303700722618</v>
       </c>
       <c r="F14" t="n">
-        <v>395.924535096324</v>
+        <v>381.2557545470806</v>
       </c>
       <c r="G14" t="n">
-        <v>389.302737515135</v>
+        <v>389.6824463205042</v>
       </c>
       <c r="H14" t="n">
-        <v>313.4748021157671</v>
+        <v>313.8545109211363</v>
       </c>
       <c r="I14" t="n">
-        <v>184.4758895704059</v>
+        <v>187.9095370861751</v>
       </c>
       <c r="J14" t="n">
-        <v>0</v>
+        <v>11.94928935461252</v>
       </c>
       <c r="K14" t="n">
         <v>0</v>
@@ -23543,16 +23543,16 @@
         <v>157.6450804554009</v>
       </c>
       <c r="F15" t="n">
-        <v>122.9150037196417</v>
+        <v>123.2494512354109</v>
       </c>
       <c r="G15" t="n">
-        <v>111.3435171632106</v>
+        <v>111.7232259685798</v>
       </c>
       <c r="H15" t="n">
-        <v>86.23544423649646</v>
+        <v>86.61515304186563</v>
       </c>
       <c r="I15" t="n">
-        <v>63.39663285141508</v>
+        <v>63.77634165678425</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -23625,16 +23625,16 @@
         <v>145.4210480229312</v>
       </c>
       <c r="G16" t="n">
-        <v>167.7167873157913</v>
+        <v>167.6941187001108</v>
       </c>
       <c r="H16" t="n">
-        <v>136.2271725074396</v>
+        <v>136.6068813128088</v>
       </c>
       <c r="I16" t="n">
-        <v>129.4504749272583</v>
+        <v>129.8301837326275</v>
       </c>
       <c r="J16" t="n">
-        <v>67.35918011667277</v>
+        <v>67.73888892204195</v>
       </c>
       <c r="K16" t="n">
         <v>0</v>
@@ -23701,19 +23701,19 @@
         <v>381.9303700722618</v>
       </c>
       <c r="F17" t="n">
-        <v>406.8760457417114</v>
+        <v>394.5240408470375</v>
       </c>
       <c r="G17" t="n">
-        <v>415.302737515135</v>
+        <v>387.7127122548189</v>
       </c>
       <c r="H17" t="n">
-        <v>339.4748021157671</v>
+        <v>311.884776855451</v>
       </c>
       <c r="I17" t="n">
-        <v>210.4758895704059</v>
+        <v>182.8858643100898</v>
       </c>
       <c r="J17" t="n">
-        <v>11.94928935461252</v>
+        <v>0</v>
       </c>
       <c r="K17" t="n">
         <v>0</v>
@@ -23734,19 +23734,19 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>9.990699214544804</v>
       </c>
       <c r="R17" t="n">
-        <v>121.8691179411497</v>
+        <v>149.8691179411497</v>
       </c>
       <c r="S17" t="n">
-        <v>181.0200695862453</v>
+        <v>209.0200695862453</v>
       </c>
       <c r="T17" t="n">
-        <v>195.0958495641314</v>
+        <v>223.0958495641314</v>
       </c>
       <c r="U17" t="n">
-        <v>236.6739521223813</v>
+        <v>251.3456529078365</v>
       </c>
       <c r="V17" t="n">
         <v>327.7522584701349</v>
@@ -23768,10 +23768,10 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>138.5331836498673</v>
+        <v>138.9431583895512</v>
       </c>
       <c r="C18" t="n">
-        <v>148.0460989883157</v>
+        <v>172.7084989883157</v>
       </c>
       <c r="D18" t="n">
         <v>147.4450655646388</v>
@@ -23816,16 +23816,16 @@
         <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>72.15783415264313</v>
+        <v>72.56780889232699</v>
       </c>
       <c r="S18" t="n">
         <v>171.6831711038378</v>
       </c>
       <c r="T18" t="n">
-        <v>200.1647286948216</v>
+        <v>175.8634344455351</v>
       </c>
       <c r="U18" t="n">
-        <v>225.9413820809748</v>
+        <v>198.3513568206587</v>
       </c>
       <c r="V18" t="n">
         <v>232.8005871494253</v>
@@ -23834,7 +23834,7 @@
         <v>251.6949831609196</v>
       </c>
       <c r="X18" t="n">
-        <v>177.7729852034775</v>
+        <v>205.7729852034775</v>
       </c>
       <c r="Y18" t="n">
         <v>205.6826957773044</v>
@@ -23892,25 +23892,25 @@
         <v>2.721440735106512</v>
       </c>
       <c r="Q19" t="n">
-        <v>64.13957562550827</v>
+        <v>86.16204325169439</v>
       </c>
       <c r="R19" t="n">
-        <v>149.2933913771695</v>
+        <v>149.7033661168533</v>
       </c>
       <c r="S19" t="n">
-        <v>224.0165980369723</v>
+        <v>196.4265727766561</v>
       </c>
       <c r="T19" t="n">
-        <v>227.9455894282815</v>
+        <v>200.3555641679654</v>
       </c>
       <c r="U19" t="n">
-        <v>286.3190293564909</v>
+        <v>263.8702699959815</v>
       </c>
       <c r="V19" t="n">
-        <v>224.137643323828</v>
+        <v>252.137643323828</v>
       </c>
       <c r="W19" t="n">
-        <v>258.522998336591</v>
+        <v>286.522998336591</v>
       </c>
       <c r="X19" t="n">
         <v>225.7096553890372</v>
@@ -23926,7 +23926,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>382.7338416634806</v>
+        <v>182.397745374651</v>
       </c>
       <c r="C20" t="n">
         <v>365.2728917710076</v>
@@ -23935,13 +23935,13 @@
         <v>354.683041620683</v>
       </c>
       <c r="E20" t="n">
-        <v>140.9303700722618</v>
+        <v>381.9303700722618</v>
       </c>
       <c r="F20" t="n">
-        <v>165.8760457417114</v>
+        <v>406.8760457417114</v>
       </c>
       <c r="G20" t="n">
-        <v>174.302737515135</v>
+        <v>415.302737515135</v>
       </c>
       <c r="H20" t="n">
         <v>339.4748021157671</v>
@@ -23950,7 +23950,7 @@
         <v>210.4758895704059</v>
       </c>
       <c r="J20" t="n">
-        <v>11.94928935461252</v>
+        <v>0</v>
       </c>
       <c r="K20" t="n">
         <v>0</v>
@@ -23989,13 +23989,13 @@
         <v>327.7522584701349</v>
       </c>
       <c r="W20" t="n">
-        <v>349.240968717413</v>
+        <v>108.226679839754</v>
       </c>
       <c r="X20" t="n">
-        <v>369.731100678469</v>
+        <v>128.71681180081</v>
       </c>
       <c r="Y20" t="n">
-        <v>173.9651386560536</v>
+        <v>145.2236497783945</v>
       </c>
     </row>
     <row r="21">
@@ -24005,31 +24005,31 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>166.5331836498673</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>172.7084989883157</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>147.4450655646388</v>
+        <v>0</v>
       </c>
       <c r="E21" t="n">
         <v>157.6450804554009</v>
       </c>
       <c r="F21" t="n">
-        <v>145.0692123933839</v>
+        <v>0</v>
       </c>
       <c r="G21" t="n">
-        <v>137.3435171632106</v>
+        <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>112.2354442364965</v>
+        <v>36.14989389716658</v>
       </c>
       <c r="I21" t="n">
-        <v>89.39663285141508</v>
+        <v>0</v>
       </c>
       <c r="J21" t="n">
-        <v>0.7465913262578567</v>
+        <v>0</v>
       </c>
       <c r="K21" t="n">
         <v>0</v>
@@ -24062,19 +24062,19 @@
         <v>200.1647286948216</v>
       </c>
       <c r="U21" t="n">
-        <v>175.924850211182</v>
+        <v>225.9413820809748</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>232.8005871494253</v>
       </c>
       <c r="W21" t="n">
-        <v>10.69498316091961</v>
+        <v>251.6949831609196</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>205.7729852034775</v>
       </c>
       <c r="Y21" t="n">
-        <v>0</v>
+        <v>205.6826957773044</v>
       </c>
     </row>
     <row r="22">
@@ -24138,10 +24138,10 @@
         <v>224.0165980369723</v>
       </c>
       <c r="T22" t="n">
-        <v>227.9455894282815</v>
+        <v>94.7586218429135</v>
       </c>
       <c r="U22" t="n">
-        <v>153.1320617711229</v>
+        <v>286.3190293564909</v>
       </c>
       <c r="V22" t="n">
         <v>252.137643323828</v>
@@ -24163,22 +24163,22 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>141.7338416634806</v>
+        <v>382.7338416634806</v>
       </c>
       <c r="C23" t="n">
-        <v>365.2728917710076</v>
+        <v>124.2586028933485</v>
       </c>
       <c r="D23" t="n">
-        <v>354.683041620683</v>
+        <v>113.6687527430239</v>
       </c>
       <c r="E23" t="n">
         <v>381.9303700722618</v>
       </c>
       <c r="F23" t="n">
-        <v>165.8760457417114</v>
+        <v>165.8617568640524</v>
       </c>
       <c r="G23" t="n">
-        <v>203.029937515135</v>
+        <v>415.302737515135</v>
       </c>
       <c r="H23" t="n">
         <v>339.4748021157671</v>
@@ -24232,7 +24232,7 @@
         <v>369.731100678469</v>
       </c>
       <c r="Y23" t="n">
-        <v>145.2379386560536</v>
+        <v>173.9525530126116</v>
       </c>
     </row>
     <row r="24">
@@ -24245,22 +24245,22 @@
         <v>166.5331836498673</v>
       </c>
       <c r="C24" t="n">
-        <v>172.7084989883157</v>
+        <v>0</v>
       </c>
       <c r="D24" t="n">
-        <v>147.4450655646388</v>
+        <v>0</v>
       </c>
       <c r="E24" t="n">
         <v>157.6450804554009</v>
       </c>
       <c r="F24" t="n">
-        <v>95.05268052359096</v>
+        <v>145.0692123933839</v>
       </c>
       <c r="G24" t="n">
-        <v>137.3435171632106</v>
+        <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>112.2354442364965</v>
+        <v>72.88755660297187</v>
       </c>
       <c r="I24" t="n">
         <v>89.39663285141508</v>
@@ -24305,10 +24305,10 @@
         <v>0</v>
       </c>
       <c r="W24" t="n">
-        <v>10.69498316091961</v>
+        <v>251.6949831609196</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>205.7729852034775</v>
       </c>
       <c r="Y24" t="n">
         <v>0</v>
@@ -24378,13 +24378,13 @@
         <v>227.9455894282815</v>
       </c>
       <c r="U25" t="n">
-        <v>286.3190293564909</v>
+        <v>153.1320617711229</v>
       </c>
       <c r="V25" t="n">
         <v>252.137643323828</v>
       </c>
       <c r="W25" t="n">
-        <v>153.336030751223</v>
+        <v>286.522998336591</v>
       </c>
       <c r="X25" t="n">
         <v>225.7096553890372</v>
@@ -24400,19 +24400,19 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>141.7338416634806</v>
+        <v>382.7338416634806</v>
       </c>
       <c r="C26" t="n">
         <v>365.2728917710076</v>
       </c>
       <c r="D26" t="n">
-        <v>354.683041620683</v>
+        <v>284.3390338194077</v>
       </c>
       <c r="E26" t="n">
-        <v>140.9303700722618</v>
+        <v>140.9160811946027</v>
       </c>
       <c r="F26" t="n">
-        <v>165.8760457417114</v>
+        <v>165.8617568640524</v>
       </c>
       <c r="G26" t="n">
         <v>415.302737515135</v>
@@ -24445,16 +24445,16 @@
         <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>9.990699214544804</v>
+        <v>0</v>
       </c>
       <c r="R26" t="n">
-        <v>149.8691179411497</v>
+        <v>0</v>
       </c>
       <c r="S26" t="n">
         <v>209.0200695862453</v>
       </c>
       <c r="T26" t="n">
-        <v>223.0958495641314</v>
+        <v>0</v>
       </c>
       <c r="U26" t="n">
         <v>251.3456529078365</v>
@@ -24469,7 +24469,7 @@
         <v>369.731100678469</v>
       </c>
       <c r="Y26" t="n">
-        <v>173.9651386560536</v>
+        <v>386.2379386560536</v>
       </c>
     </row>
     <row r="27">
@@ -24485,10 +24485,10 @@
         <v>172.7084989883157</v>
       </c>
       <c r="D27" t="n">
-        <v>147.4450655646388</v>
+        <v>36.88229339707597</v>
       </c>
       <c r="E27" t="n">
-        <v>157.6450804554009</v>
+        <v>0</v>
       </c>
       <c r="F27" t="n">
         <v>145.0692123933839</v>
@@ -24503,7 +24503,7 @@
         <v>89.39663285141508</v>
       </c>
       <c r="J27" t="n">
-        <v>0</v>
+        <v>0.7465913262578567</v>
       </c>
       <c r="K27" t="n">
         <v>0</v>
@@ -24536,19 +24536,19 @@
         <v>0</v>
       </c>
       <c r="U27" t="n">
-        <v>144.0355830828363</v>
+        <v>0</v>
       </c>
       <c r="V27" t="n">
         <v>232.8005871494253</v>
       </c>
       <c r="W27" t="n">
-        <v>10.69498316091961</v>
+        <v>10.68069428326055</v>
       </c>
       <c r="X27" t="n">
-        <v>0</v>
+        <v>205.7729852034775</v>
       </c>
       <c r="Y27" t="n">
-        <v>0</v>
+        <v>205.6826957773044</v>
       </c>
     </row>
     <row r="28">
@@ -24637,10 +24637,10 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>170.4610416634806</v>
+        <v>382.7338416634806</v>
       </c>
       <c r="C29" t="n">
-        <v>365.2728917710076</v>
+        <v>124.2586028933485</v>
       </c>
       <c r="D29" t="n">
         <v>354.683041620683</v>
@@ -24649,13 +24649,13 @@
         <v>381.9303700722618</v>
       </c>
       <c r="F29" t="n">
-        <v>165.8760457417114</v>
+        <v>406.8760457417114</v>
       </c>
       <c r="G29" t="n">
-        <v>174.302737515135</v>
+        <v>415.302737515135</v>
       </c>
       <c r="H29" t="n">
-        <v>339.4748021157671</v>
+        <v>98.46051323810809</v>
       </c>
       <c r="I29" t="n">
         <v>210.4758895704059</v>
@@ -24685,10 +24685,10 @@
         <v>9.990699214544804</v>
       </c>
       <c r="R29" t="n">
-        <v>149.8691179411497</v>
+        <v>0</v>
       </c>
       <c r="S29" t="n">
-        <v>209.0200695862453</v>
+        <v>146.6038018839531</v>
       </c>
       <c r="T29" t="n">
         <v>223.0958495641314</v>
@@ -24703,10 +24703,10 @@
         <v>349.240968717413</v>
       </c>
       <c r="X29" t="n">
-        <v>369.731100678469</v>
+        <v>128.71681180081</v>
       </c>
       <c r="Y29" t="n">
-        <v>145.2379386560536</v>
+        <v>386.2379386560536</v>
       </c>
     </row>
     <row r="30">
@@ -24719,28 +24719,28 @@
         <v>166.5331836498673</v>
       </c>
       <c r="C30" t="n">
-        <v>172.7084989883157</v>
+        <v>0</v>
       </c>
       <c r="D30" t="n">
         <v>147.4450655646388</v>
       </c>
       <c r="E30" t="n">
-        <v>122.2789783806227</v>
+        <v>157.6450804554009</v>
       </c>
       <c r="F30" t="n">
         <v>145.0692123933839</v>
       </c>
       <c r="G30" t="n">
-        <v>137.3435171632106</v>
+        <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>112.2354442364965</v>
+        <v>0</v>
       </c>
       <c r="I30" t="n">
-        <v>89.39663285141508</v>
+        <v>50.91730831636087</v>
       </c>
       <c r="J30" t="n">
-        <v>0.7465913262578567</v>
+        <v>0</v>
       </c>
       <c r="K30" t="n">
         <v>0</v>
@@ -24770,16 +24770,16 @@
         <v>171.6831711038378</v>
       </c>
       <c r="T30" t="n">
-        <v>0</v>
+        <v>200.1647286948216</v>
       </c>
       <c r="U30" t="n">
-        <v>0</v>
+        <v>225.9413820809748</v>
       </c>
       <c r="V30" t="n">
         <v>0</v>
       </c>
       <c r="W30" t="n">
-        <v>10.69498316091961</v>
+        <v>10.68069428326055</v>
       </c>
       <c r="X30" t="n">
         <v>205.7729852034775</v>
@@ -24892,7 +24892,7 @@
         <v>415.302737515135</v>
       </c>
       <c r="H32" t="n">
-        <v>124.4748021157671</v>
+        <v>124.0808044327389</v>
       </c>
       <c r="I32" t="n">
         <v>210.4758895704059</v>
@@ -24919,28 +24919,28 @@
         <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>9.990699214544804</v>
+        <v>0</v>
       </c>
       <c r="R32" t="n">
-        <v>149.8691179411497</v>
+        <v>0</v>
       </c>
       <c r="S32" t="n">
-        <v>209.0200695862453</v>
+        <v>179.1608535827286</v>
       </c>
       <c r="T32" t="n">
-        <v>223.0958495641314</v>
+        <v>7.701851881103124</v>
       </c>
       <c r="U32" t="n">
-        <v>36.3456529078365</v>
+        <v>35.95165522480826</v>
       </c>
       <c r="V32" t="n">
-        <v>138.3802584701349</v>
+        <v>327.7522584701349</v>
       </c>
       <c r="W32" t="n">
         <v>349.240968717413</v>
       </c>
       <c r="X32" t="n">
-        <v>154.731100678469</v>
+        <v>369.731100678469</v>
       </c>
       <c r="Y32" t="n">
         <v>386.2379386560536</v>
@@ -24953,10 +24953,10 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>56.22834001230495</v>
+        <v>166.5331836498673</v>
       </c>
       <c r="C33" t="n">
-        <v>172.7084989883157</v>
+        <v>0</v>
       </c>
       <c r="D33" t="n">
         <v>147.4450655646388</v>
@@ -24965,19 +24965,19 @@
         <v>157.6450804554009</v>
       </c>
       <c r="F33" t="n">
-        <v>0</v>
+        <v>145.0692123933839</v>
       </c>
       <c r="G33" t="n">
-        <v>137.3435171632106</v>
+        <v>5.843410788187981</v>
       </c>
       <c r="H33" t="n">
-        <v>0</v>
+        <v>112.2354442364965</v>
       </c>
       <c r="I33" t="n">
-        <v>0</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="J33" t="n">
-        <v>0.7465913262578567</v>
+        <v>0</v>
       </c>
       <c r="K33" t="n">
         <v>0</v>
@@ -25001,28 +25001,28 @@
         <v>0</v>
       </c>
       <c r="R33" t="n">
-        <v>100.1578341526431</v>
+        <v>0</v>
       </c>
       <c r="S33" t="n">
-        <v>0</v>
+        <v>171.6831711038378</v>
       </c>
       <c r="T33" t="n">
         <v>200.1647286948216</v>
       </c>
       <c r="U33" t="n">
-        <v>225.9413820809748</v>
+        <v>10.54738439794659</v>
       </c>
       <c r="V33" t="n">
         <v>232.8005871494253</v>
       </c>
       <c r="W33" t="n">
-        <v>251.6949831609196</v>
+        <v>36.30098547789137</v>
       </c>
       <c r="X33" t="n">
         <v>205.7729852034775</v>
       </c>
       <c r="Y33" t="n">
-        <v>0</v>
+        <v>205.6826957773044</v>
       </c>
     </row>
     <row r="34">
@@ -25050,13 +25050,13 @@
         <v>167.9909793584588</v>
       </c>
       <c r="H34" t="n">
-        <v>122.3993850387443</v>
+        <v>162.2271725074396</v>
       </c>
       <c r="I34" t="n">
         <v>155.4504749272583</v>
       </c>
       <c r="J34" t="n">
-        <v>0</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="K34" t="n">
         <v>22.26949182588285</v>
@@ -25101,7 +25101,7 @@
         <v>225.7096553890372</v>
       </c>
       <c r="Y34" t="n">
-        <v>218.5846533520948</v>
+        <v>85.3976857667268</v>
       </c>
     </row>
     <row r="35">
@@ -25111,16 +25111,16 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>193.3618416634806</v>
+        <v>382.7338416634806</v>
       </c>
       <c r="C35" t="n">
-        <v>150.2728917710076</v>
+        <v>149.8788940879793</v>
       </c>
       <c r="D35" t="n">
         <v>354.683041620683</v>
       </c>
       <c r="E35" t="n">
-        <v>166.9303700722618</v>
+        <v>381.9303700722618</v>
       </c>
       <c r="F35" t="n">
         <v>406.8760457417114</v>
@@ -25129,13 +25129,13 @@
         <v>415.302737515135</v>
       </c>
       <c r="H35" t="n">
-        <v>124.4748021157671</v>
+        <v>339.4748021157671</v>
       </c>
       <c r="I35" t="n">
-        <v>210.4758895704059</v>
+        <v>42.69684498035204</v>
       </c>
       <c r="J35" t="n">
-        <v>11.94928935461252</v>
+        <v>0</v>
       </c>
       <c r="K35" t="n">
         <v>0</v>
@@ -25156,7 +25156,7 @@
         <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>9.990699214544804</v>
+        <v>0</v>
       </c>
       <c r="R35" t="n">
         <v>149.8691179411497</v>
@@ -25168,10 +25168,10 @@
         <v>223.0958495641314</v>
       </c>
       <c r="U35" t="n">
-        <v>251.3456529078365</v>
+        <v>35.95165522480826</v>
       </c>
       <c r="V35" t="n">
-        <v>327.7522584701349</v>
+        <v>112.3582607871067</v>
       </c>
       <c r="W35" t="n">
         <v>349.240968717413</v>
@@ -25196,16 +25196,16 @@
         <v>172.7084989883157</v>
       </c>
       <c r="D36" t="n">
-        <v>147.4450655646388</v>
+        <v>0</v>
       </c>
       <c r="E36" t="n">
-        <v>157.6450804554009</v>
+        <v>0</v>
       </c>
       <c r="F36" t="n">
         <v>145.0692123933839</v>
       </c>
       <c r="G36" t="n">
-        <v>137.3435171632106</v>
+        <v>0</v>
       </c>
       <c r="H36" t="n">
         <v>112.2354442364965</v>
@@ -25214,7 +25214,7 @@
         <v>89.39663285141508</v>
       </c>
       <c r="J36" t="n">
-        <v>0</v>
+        <v>0.7465913262578567</v>
       </c>
       <c r="K36" t="n">
         <v>0</v>
@@ -25244,22 +25244,22 @@
         <v>171.6831711038378</v>
       </c>
       <c r="T36" t="n">
-        <v>11.53932002107956</v>
+        <v>200.1647286948216</v>
       </c>
       <c r="U36" t="n">
-        <v>10.94138208097482</v>
+        <v>225.9413820809748</v>
       </c>
       <c r="V36" t="n">
-        <v>17.80058714942527</v>
+        <v>232.8005871494253</v>
       </c>
       <c r="W36" t="n">
-        <v>36.69498316091961</v>
+        <v>36.30098547789137</v>
       </c>
       <c r="X36" t="n">
         <v>205.7729852034775</v>
       </c>
       <c r="Y36" t="n">
-        <v>205.6826957773044</v>
+        <v>27.60933043528701</v>
       </c>
     </row>
     <row r="37">
@@ -25311,13 +25311,13 @@
         <v>0</v>
       </c>
       <c r="P37" t="n">
-        <v>0</v>
+        <v>2.721440735106512</v>
       </c>
       <c r="Q37" t="n">
-        <v>0</v>
+        <v>86.16204325169439</v>
       </c>
       <c r="R37" t="n">
-        <v>132.9899077786023</v>
+        <v>177.2933913771695</v>
       </c>
       <c r="S37" t="n">
         <v>224.0165980369723</v>
@@ -25332,7 +25332,7 @@
         <v>252.137643323828</v>
       </c>
       <c r="W37" t="n">
-        <v>286.522998336591</v>
+        <v>153.336030751223</v>
       </c>
       <c r="X37" t="n">
         <v>225.7096553890372</v>
@@ -25348,10 +25348,10 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>167.7338416634806</v>
+        <v>382.7338416634806</v>
       </c>
       <c r="C38" t="n">
-        <v>175.9008917710076</v>
+        <v>365.2728917710076</v>
       </c>
       <c r="D38" t="n">
         <v>354.683041620683</v>
@@ -25363,7 +25363,7 @@
         <v>406.8760457417114</v>
       </c>
       <c r="G38" t="n">
-        <v>200.302737515135</v>
+        <v>415.302737515135</v>
       </c>
       <c r="H38" t="n">
         <v>339.4748021157671</v>
@@ -25396,28 +25396,28 @@
         <v>9.990699214544804</v>
       </c>
       <c r="R38" t="n">
-        <v>149.8691179411497</v>
+        <v>0</v>
       </c>
       <c r="S38" t="n">
-        <v>209.0200695862453</v>
+        <v>0</v>
       </c>
       <c r="T38" t="n">
         <v>223.0958495641314</v>
       </c>
       <c r="U38" t="n">
-        <v>251.3456529078365</v>
+        <v>35.95165522480826</v>
       </c>
       <c r="V38" t="n">
-        <v>327.7522584701349</v>
+        <v>112.3582607871067</v>
       </c>
       <c r="W38" t="n">
-        <v>349.240968717413</v>
+        <v>303.0171254025686</v>
       </c>
       <c r="X38" t="n">
         <v>369.731100678469</v>
       </c>
       <c r="Y38" t="n">
-        <v>171.2379386560536</v>
+        <v>386.2379386560536</v>
       </c>
     </row>
     <row r="39">
@@ -25433,7 +25433,7 @@
         <v>172.7084989883157</v>
       </c>
       <c r="D39" t="n">
-        <v>0</v>
+        <v>147.4450655646388</v>
       </c>
       <c r="E39" t="n">
         <v>157.6450804554009</v>
@@ -25481,22 +25481,22 @@
         <v>171.6831711038378</v>
       </c>
       <c r="T39" t="n">
-        <v>0</v>
+        <v>200.1647286948216</v>
       </c>
       <c r="U39" t="n">
-        <v>225.9413820809748</v>
+        <v>10.54738439794659</v>
       </c>
       <c r="V39" t="n">
-        <v>17.80058714942527</v>
+        <v>17.40658946639704</v>
       </c>
       <c r="W39" t="n">
         <v>251.6949831609196</v>
       </c>
       <c r="X39" t="n">
-        <v>139.6934752402423</v>
+        <v>0</v>
       </c>
       <c r="Y39" t="n">
-        <v>0</v>
+        <v>6.342650138542439</v>
       </c>
     </row>
     <row r="40">
@@ -25548,13 +25548,13 @@
         <v>0</v>
       </c>
       <c r="P40" t="n">
-        <v>0</v>
+        <v>2.721440735106512</v>
       </c>
       <c r="Q40" t="n">
-        <v>0</v>
+        <v>86.16204325169439</v>
       </c>
       <c r="R40" t="n">
-        <v>132.9899077786023</v>
+        <v>177.2933913771695</v>
       </c>
       <c r="S40" t="n">
         <v>224.0165980369723</v>
@@ -25563,7 +25563,7 @@
         <v>227.9455894282815</v>
       </c>
       <c r="U40" t="n">
-        <v>286.3190293564909</v>
+        <v>153.1320617711229</v>
       </c>
       <c r="V40" t="n">
         <v>252.137643323828</v>
@@ -25585,13 +25585,13 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>169.7338416634806</v>
+        <v>382.7338416634806</v>
       </c>
       <c r="C41" t="n">
-        <v>365.2728917710076</v>
+        <v>151.8486281536646</v>
       </c>
       <c r="D41" t="n">
-        <v>354.683041620683</v>
+        <v>141.25877800334</v>
       </c>
       <c r="E41" t="n">
         <v>381.9303700722618</v>
@@ -25600,16 +25600,16 @@
         <v>406.8760457417114</v>
       </c>
       <c r="G41" t="n">
-        <v>227.692337515135</v>
+        <v>415.302737515135</v>
       </c>
       <c r="H41" t="n">
-        <v>339.4748021157671</v>
+        <v>126.0505384984242</v>
       </c>
       <c r="I41" t="n">
         <v>210.4758895704059</v>
       </c>
       <c r="J41" t="n">
-        <v>11.94928935461252</v>
+        <v>0</v>
       </c>
       <c r="K41" t="n">
         <v>0</v>
@@ -25630,7 +25630,7 @@
         <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>9.990699214544804</v>
+        <v>0</v>
       </c>
       <c r="R41" t="n">
         <v>149.8691179411497</v>
@@ -25642,16 +25642,16 @@
         <v>223.0958495641314</v>
       </c>
       <c r="U41" t="n">
-        <v>251.3456529078365</v>
+        <v>85.30155008283819</v>
       </c>
       <c r="V41" t="n">
         <v>327.7522584701349</v>
       </c>
       <c r="W41" t="n">
-        <v>136.240968717413</v>
+        <v>349.240968717413</v>
       </c>
       <c r="X41" t="n">
-        <v>156.731100678469</v>
+        <v>369.731100678469</v>
       </c>
       <c r="Y41" t="n">
         <v>386.2379386560536</v>
@@ -25688,7 +25688,7 @@
         <v>89.39663285141508</v>
       </c>
       <c r="J42" t="n">
-        <v>0</v>
+        <v>0.7465913262578567</v>
       </c>
       <c r="K42" t="n">
         <v>0</v>
@@ -25721,16 +25721,16 @@
         <v>200.1647286948216</v>
       </c>
       <c r="U42" t="n">
-        <v>12.94138208097482</v>
+        <v>12.5171184636319</v>
       </c>
       <c r="V42" t="n">
-        <v>19.80058714942527</v>
+        <v>19.37632353208235</v>
       </c>
       <c r="W42" t="n">
-        <v>38.69498316091961</v>
+        <v>38.27071954357669</v>
       </c>
       <c r="X42" t="n">
-        <v>18.9091765297353</v>
+        <v>17.78889380932185</v>
       </c>
       <c r="Y42" t="n">
         <v>205.6826957773044</v>
@@ -25749,7 +25749,7 @@
         <v>167.2468210986278</v>
       </c>
       <c r="D43" t="n">
-        <v>15.42850543284436</v>
+        <v>148.6154730182124</v>
       </c>
       <c r="E43" t="n">
         <v>146.4339626465692</v>
@@ -25791,7 +25791,7 @@
         <v>86.16204325169439</v>
       </c>
       <c r="R43" t="n">
-        <v>177.2933913771695</v>
+        <v>44.10642379180149</v>
       </c>
       <c r="S43" t="n">
         <v>224.0165980369723</v>
@@ -26094,7 +26094,7 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>350350.0795405007</v>
+        <v>350035.0587549793</v>
       </c>
     </row>
     <row r="5">
@@ -26102,7 +26102,7 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>350350.0795405005</v>
+        <v>350035.0587549793</v>
       </c>
     </row>
     <row r="6">
@@ -26110,7 +26110,7 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>350350.0795405007</v>
+        <v>350035.0587549795</v>
       </c>
     </row>
     <row r="7">
@@ -26118,7 +26118,7 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>351994.6487060303</v>
+        <v>351669.2246312143</v>
       </c>
     </row>
     <row r="8">
@@ -26126,7 +26126,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>506779.7343245362</v>
+        <v>506790.0512205642</v>
       </c>
     </row>
     <row r="9">
@@ -26134,7 +26134,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>506779.7343245363</v>
+        <v>506790.0512205641</v>
       </c>
     </row>
     <row r="10">
@@ -26142,7 +26142,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>506779.7343245363</v>
+        <v>506790.0512205641</v>
       </c>
     </row>
     <row r="11">
@@ -26150,7 +26150,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>506779.7343245363</v>
+        <v>506790.0512205642</v>
       </c>
     </row>
     <row r="12">
@@ -26158,7 +26158,7 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>488007.1404845365</v>
+        <v>488291.6158105898</v>
       </c>
     </row>
     <row r="13">
@@ -26166,7 +26166,7 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>488007.1404845365</v>
+        <v>488291.6158105899</v>
       </c>
     </row>
     <row r="14">
@@ -26174,7 +26174,7 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>488007.1404845365</v>
+        <v>488291.6158105897</v>
       </c>
     </row>
     <row r="15">
@@ -26182,7 +26182,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>486563.0948045364</v>
+        <v>486869.422826439</v>
       </c>
     </row>
     <row r="16">
@@ -26267,40 +26267,40 @@
         <v>48378.33248915088</v>
       </c>
       <c r="D2" t="n">
-        <v>51690.99534204105</v>
+        <v>51644.51686548872</v>
       </c>
       <c r="E2" t="n">
-        <v>51690.99534204105</v>
+        <v>51644.51686548872</v>
       </c>
       <c r="F2" t="n">
-        <v>51690.99534204105</v>
+        <v>51644.51686548872</v>
       </c>
       <c r="G2" t="n">
-        <v>51933.63669433229</v>
+        <v>51885.6233062447</v>
       </c>
       <c r="H2" t="n">
-        <v>74770.78047411185</v>
+        <v>74772.30263909958</v>
       </c>
       <c r="I2" t="n">
-        <v>74770.78047411185</v>
+        <v>74772.30263909959</v>
       </c>
       <c r="J2" t="n">
-        <v>74770.78047411187</v>
+        <v>74772.30263909958</v>
       </c>
       <c r="K2" t="n">
-        <v>74770.78047411186</v>
+        <v>74772.30263909958</v>
       </c>
       <c r="L2" t="n">
-        <v>72001.05351411189</v>
+        <v>72043.02528352961</v>
       </c>
       <c r="M2" t="n">
-        <v>72001.05351411185</v>
+        <v>72043.0252835296</v>
       </c>
       <c r="N2" t="n">
-        <v>72001.05351411185</v>
+        <v>72043.0252835296</v>
       </c>
       <c r="O2" t="n">
-        <v>71787.99759411186</v>
+        <v>71833.1935317696</v>
       </c>
       <c r="P2" t="n">
         <v>48378.33248915088</v>
@@ -26319,7 +26319,7 @@
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>8076.38</v>
+        <v>7958.431053788175</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
@@ -26328,10 +26328,10 @@
         <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>548.1700000000001</v>
+        <v>539.8745613933579</v>
       </c>
       <c r="H3" t="n">
-        <v>57469.317</v>
+        <v>57583.78714233168</v>
       </c>
       <c r="I3" t="n">
         <v>0</v>
@@ -26371,40 +26371,40 @@
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>22.532822180663</v>
+        <v>22.21667432804714</v>
       </c>
       <c r="E4" t="n">
-        <v>22.532822180663</v>
+        <v>22.21667432804715</v>
       </c>
       <c r="F4" t="n">
-        <v>22.532822180663</v>
+        <v>22.21667432804715</v>
       </c>
       <c r="G4" t="n">
-        <v>24.18327521124651</v>
+        <v>23.85668684891895</v>
       </c>
       <c r="H4" t="n">
-        <v>179.5221438966159</v>
+        <v>179.5324977039669</v>
       </c>
       <c r="I4" t="n">
-        <v>179.5221438966159</v>
+        <v>179.5324977039669</v>
       </c>
       <c r="J4" t="n">
-        <v>179.5221438966159</v>
+        <v>179.5324977039669</v>
       </c>
       <c r="K4" t="n">
-        <v>179.5221438966159</v>
+        <v>179.5324977039669</v>
       </c>
       <c r="L4" t="n">
-        <v>160.6823863208583</v>
+        <v>160.9678794298453</v>
       </c>
       <c r="M4" t="n">
-        <v>160.6823863208583</v>
+        <v>160.9678794298453</v>
       </c>
       <c r="N4" t="n">
-        <v>160.6823863208583</v>
+        <v>160.9678794298453</v>
       </c>
       <c r="O4" t="n">
-        <v>159.2331741996462</v>
+        <v>159.5405981880675</v>
       </c>
       <c r="P4" t="n">
         <v>0</v>
@@ -26423,40 +26423,40 @@
         <v>33627.6</v>
       </c>
       <c r="D5" t="n">
-        <v>35208.4</v>
+        <v>35185.31370463355</v>
       </c>
       <c r="E5" t="n">
-        <v>1580.8</v>
+        <v>1557.713704633554</v>
       </c>
       <c r="F5" t="n">
-        <v>1580.8</v>
+        <v>1557.713704633554</v>
       </c>
       <c r="G5" t="n">
-        <v>1702.4</v>
+        <v>1677.473535827221</v>
       </c>
       <c r="H5" t="n">
-        <v>14652.8</v>
+        <v>14653.66876376167</v>
       </c>
       <c r="I5" t="n">
-        <v>14652.8</v>
+        <v>14653.66876376167</v>
       </c>
       <c r="J5" t="n">
-        <v>14652.8</v>
+        <v>14653.66876376167</v>
       </c>
       <c r="K5" t="n">
-        <v>14652.8</v>
+        <v>14653.66876376167</v>
       </c>
       <c r="L5" t="n">
-        <v>13072</v>
+        <v>13095.95505912812</v>
       </c>
       <c r="M5" t="n">
-        <v>13072</v>
+        <v>13095.95505912812</v>
       </c>
       <c r="N5" t="n">
-        <v>13072</v>
+        <v>13095.95505912812</v>
       </c>
       <c r="O5" t="n">
-        <v>12950.4</v>
+        <v>12976.19522793445</v>
       </c>
       <c r="P5" t="n">
         <v>0</v>
@@ -26469,46 +26469,46 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>14750.73248915088</v>
+        <v>14750.73248915087</v>
       </c>
       <c r="C6" t="n">
         <v>14750.73248915088</v>
       </c>
       <c r="D6" t="n">
-        <v>8383.682519860384</v>
+        <v>8478.55543273894</v>
       </c>
       <c r="E6" t="n">
-        <v>50087.66251986039</v>
+        <v>50064.58648652711</v>
       </c>
       <c r="F6" t="n">
-        <v>50087.66251986038</v>
+        <v>50064.58648652711</v>
       </c>
       <c r="G6" t="n">
-        <v>49658.88341912105</v>
+        <v>49644.4185221752</v>
       </c>
       <c r="H6" t="n">
-        <v>2469.141330215229</v>
+        <v>2355.314235302259</v>
       </c>
       <c r="I6" t="n">
-        <v>59938.45833021523</v>
+        <v>59939.10137763395</v>
       </c>
       <c r="J6" t="n">
-        <v>59938.45833021526</v>
+        <v>59939.10137763394</v>
       </c>
       <c r="K6" t="n">
-        <v>59938.45833021525</v>
+        <v>59939.10137763394</v>
       </c>
       <c r="L6" t="n">
-        <v>58768.37112779103</v>
+        <v>58786.10234497164</v>
       </c>
       <c r="M6" t="n">
-        <v>58768.37112779099</v>
+        <v>58786.10234497163</v>
       </c>
       <c r="N6" t="n">
-        <v>58768.37112779099</v>
+        <v>58786.10234497163</v>
       </c>
       <c r="O6" t="n">
-        <v>58678.36441991221</v>
+        <v>58697.4577056471</v>
       </c>
       <c r="P6" t="n">
         <v>48378.33248915088</v>
@@ -26733,40 +26733,40 @@
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>26</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="E4" t="n">
-        <v>26</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="F4" t="n">
-        <v>26</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="G4" t="n">
-        <v>28</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="H4" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="I4" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="J4" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="K4" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="L4" t="n">
-        <v>215</v>
+        <v>215.3939976830282</v>
       </c>
       <c r="M4" t="n">
-        <v>215</v>
+        <v>215.3939976830282</v>
       </c>
       <c r="N4" t="n">
-        <v>215</v>
+        <v>215.3939976830282</v>
       </c>
       <c r="O4" t="n">
-        <v>213</v>
+        <v>213.4242636173429</v>
       </c>
       <c r="P4" t="n">
         <v>0</v>
@@ -26840,49 +26840,49 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="C2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="N2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -26892,13 +26892,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="C3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
@@ -26910,31 +26910,31 @@
         <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I3" t="n">
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -26950,19 +26950,19 @@
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>26</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>2</v>
+        <v>1.969734065685309</v>
       </c>
       <c r="H4" t="n">
-        <v>213</v>
+        <v>213.4242636173429</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
@@ -26971,22 +26971,22 @@
         <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -27191,7 +27191,7 @@
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>26</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="M4" t="n">
         <v>0</v>
@@ -27200,10 +27200,10 @@
         <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>2</v>
+        <v>1.969734065685309</v>
       </c>
       <c r="P4" t="n">
-        <v>213</v>
+        <v>213.4242636173429</v>
       </c>
     </row>
   </sheetData>
@@ -35088,13 +35088,13 @@
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>26</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="L8" t="n">
-        <v>26</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="M8" t="n">
-        <v>24.94949494949495</v>
+        <v>24.58512791403969</v>
       </c>
       <c r="N8" t="n">
         <v>0</v>
@@ -35103,7 +35103,7 @@
         <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>26</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -35167,25 +35167,25 @@
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>24.94949494949496</v>
+        <v>0</v>
       </c>
       <c r="L9" t="n">
         <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="N9" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>26</v>
+        <v>24.58512791403969</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="Q9" t="n">
-        <v>26</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="R9" t="n">
         <v>0</v>
@@ -35249,16 +35249,16 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>26</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="M10" t="n">
-        <v>26</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="N10" t="n">
-        <v>26</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="O10" t="n">
-        <v>24.58512791403967</v>
+        <v>24.58512791403969</v>
       </c>
       <c r="P10" t="n">
         <v>0</v>
@@ -35325,22 +35325,22 @@
         <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="L11" t="n">
-        <v>24.94949494949496</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="M11" t="n">
         <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>26</v>
+        <v>24.58512791403969</v>
       </c>
       <c r="P11" t="n">
-        <v>26</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
@@ -35407,22 +35407,22 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>26</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="M12" t="n">
-        <v>26</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="N12" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>24.94949494949495</v>
+        <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>24.58512791403969</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="R12" t="n">
         <v>0</v>
@@ -35486,13 +35486,13 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>26</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="M13" t="n">
-        <v>26</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="N13" t="n">
-        <v>26</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="O13" t="n">
         <v>24.58512791403967</v>
@@ -35562,22 +35562,22 @@
         <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="L14" t="n">
-        <v>26</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="M14" t="n">
-        <v>26</v>
+        <v>24.58512791403969</v>
       </c>
       <c r="N14" t="n">
-        <v>24.94949494949495</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
@@ -35641,25 +35641,25 @@
         <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>24.94949494949496</v>
+        <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="N15" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>26</v>
+        <v>24.58512791403969</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="R15" t="n">
         <v>0</v>
@@ -35723,13 +35723,13 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>26</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="M16" t="n">
-        <v>26</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="N16" t="n">
-        <v>26</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="O16" t="n">
         <v>24.58512791403967</v>
@@ -35799,22 +35799,22 @@
         <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>28</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="L17" t="n">
-        <v>26.86868686868687</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>26.47527676494983</v>
       </c>
       <c r="O17" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
@@ -35878,25 +35878,25 @@
         <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>28</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="L18" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>26.86868686868687</v>
+        <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="O18" t="n">
-        <v>0</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>26.47527676494983</v>
       </c>
       <c r="Q18" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
         <v>0</v>
@@ -35963,10 +35963,10 @@
         <v>27.59002526031614</v>
       </c>
       <c r="M19" t="n">
-        <v>28</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="N19" t="n">
-        <v>28</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="O19" t="n">
         <v>24.58512791403967</v>
@@ -36036,7 +36036,7 @@
         <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>103.9989833439383</v>
+        <v>104.0555615261842</v>
       </c>
       <c r="L20" t="n">
         <v>181.8947995804632</v>
@@ -36118,22 +36118,22 @@
         <v>0</v>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>232.285965523585</v>
       </c>
       <c r="M21" t="n">
-        <v>217.6787513871916</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="N21" t="n">
-        <v>241</v>
+        <v>240.0046611659691</v>
       </c>
       <c r="O21" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="P21" t="n">
-        <v>184.4883612256069</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>70.09551364982758</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
         <v>0</v>
@@ -36273,7 +36273,7 @@
         <v>0</v>
       </c>
       <c r="K23" t="n">
-        <v>103.9989833439383</v>
+        <v>104.0555615261842</v>
       </c>
       <c r="L23" t="n">
         <v>181.8947995804632</v>
@@ -36352,25 +36352,25 @@
         <v>0</v>
       </c>
       <c r="K24" t="n">
-        <v>126.6237980382196</v>
+        <v>0</v>
       </c>
       <c r="L24" t="n">
-        <v>232.285965523585</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>241</v>
+        <v>217.7067518141195</v>
       </c>
       <c r="N24" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="O24" t="n">
-        <v>113.3528627008217</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="P24" t="n">
-        <v>0</v>
+        <v>184.4883612256069</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>70.09551364982758</v>
       </c>
       <c r="R24" t="n">
         <v>0</v>
@@ -36510,7 +36510,7 @@
         <v>0</v>
       </c>
       <c r="K26" t="n">
-        <v>103.9989833439383</v>
+        <v>104.0555615261842</v>
       </c>
       <c r="L26" t="n">
         <v>181.8947995804632</v>
@@ -36589,22 +36589,22 @@
         <v>0</v>
       </c>
       <c r="K27" t="n">
-        <v>0</v>
+        <v>126.6237980382196</v>
       </c>
       <c r="L27" t="n">
-        <v>46.77426503701933</v>
+        <v>232.285965523585</v>
       </c>
       <c r="M27" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="N27" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="O27" t="n">
-        <v>241</v>
+        <v>113.3808631277494</v>
       </c>
       <c r="P27" t="n">
-        <v>184.4883612256069</v>
+        <v>0</v>
       </c>
       <c r="Q27" t="n">
         <v>0</v>
@@ -36762,7 +36762,7 @@
         <v>150.7019698410586</v>
       </c>
       <c r="P29" t="n">
-        <v>90.50913423396717</v>
+        <v>90.5657124162131</v>
       </c>
       <c r="Q29" t="n">
         <v>0</v>
@@ -36826,25 +36826,25 @@
         <v>0</v>
       </c>
       <c r="K30" t="n">
-        <v>0</v>
+        <v>126.6237980382196</v>
       </c>
       <c r="L30" t="n">
-        <v>0</v>
+        <v>232.285965523585</v>
       </c>
       <c r="M30" t="n">
-        <v>217.6787513871916</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="N30" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="O30" t="n">
-        <v>241</v>
+        <v>113.3808631277494</v>
       </c>
       <c r="P30" t="n">
-        <v>184.4883612256069</v>
+        <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>70.09551364982758</v>
+        <v>0</v>
       </c>
       <c r="R30" t="n">
         <v>0</v>
@@ -36984,13 +36984,13 @@
         <v>0</v>
       </c>
       <c r="K32" t="n">
-        <v>5.216788660003122</v>
+        <v>104.0555615261842</v>
       </c>
       <c r="L32" t="n">
         <v>181.8947995804632</v>
       </c>
       <c r="M32" t="n">
-        <v>215</v>
+        <v>117.7212987676277</v>
       </c>
       <c r="N32" t="n">
         <v>207.9338608153932</v>
@@ -37066,22 +37066,22 @@
         <v>126.6237980382196</v>
       </c>
       <c r="L33" t="n">
-        <v>215</v>
+        <v>215.3939976830282</v>
       </c>
       <c r="M33" t="n">
-        <v>215</v>
+        <v>110.973048317057</v>
       </c>
       <c r="N33" t="n">
-        <v>9.59381962508408</v>
+        <v>0</v>
       </c>
       <c r="O33" t="n">
-        <v>215</v>
+        <v>215.3939976830282</v>
       </c>
       <c r="P33" t="n">
-        <v>0</v>
+        <v>184.4883612256069</v>
       </c>
       <c r="Q33" t="n">
-        <v>70.09551364982758</v>
+        <v>0</v>
       </c>
       <c r="R33" t="n">
         <v>0</v>
@@ -37227,10 +37227,10 @@
         <v>181.8947995804632</v>
       </c>
       <c r="M35" t="n">
-        <v>116.1612271338189</v>
+        <v>215.3939976830282</v>
       </c>
       <c r="N35" t="n">
-        <v>207.9338608153932</v>
+        <v>110.2611618999926</v>
       </c>
       <c r="O35" t="n">
         <v>150.7019698410586</v>
@@ -37303,22 +37303,22 @@
         <v>0</v>
       </c>
       <c r="L36" t="n">
-        <v>215</v>
+        <v>215.3939976830282</v>
       </c>
       <c r="M36" t="n">
-        <v>0</v>
+        <v>215.3939976830282</v>
       </c>
       <c r="N36" t="n">
-        <v>215</v>
+        <v>136.5956962480277</v>
       </c>
       <c r="O36" t="n">
-        <v>215</v>
+        <v>215.3939976830282</v>
       </c>
       <c r="P36" t="n">
-        <v>184.4883612256069</v>
+        <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>21.82477008752445</v>
+        <v>70.09551364982758</v>
       </c>
       <c r="R36" t="n">
         <v>0</v>
@@ -37464,7 +37464,7 @@
         <v>181.8947995804632</v>
       </c>
       <c r="M38" t="n">
-        <v>116.1612271338189</v>
+        <v>117.7212987676277</v>
       </c>
       <c r="N38" t="n">
         <v>207.9338608153932</v>
@@ -37537,25 +37537,25 @@
         <v>0</v>
       </c>
       <c r="K39" t="n">
-        <v>0</v>
+        <v>126.6237980382196</v>
       </c>
       <c r="L39" t="n">
-        <v>215</v>
+        <v>215.3939976830282</v>
       </c>
       <c r="M39" t="n">
-        <v>215</v>
+        <v>0</v>
       </c>
       <c r="N39" t="n">
-        <v>206.3131313131313</v>
+        <v>40.87753466722953</v>
       </c>
       <c r="O39" t="n">
-        <v>215</v>
+        <v>215.3939976830282</v>
       </c>
       <c r="P39" t="n">
-        <v>0</v>
+        <v>184.4883612256069</v>
       </c>
       <c r="Q39" t="n">
-        <v>0</v>
+        <v>70.09551364982758</v>
       </c>
       <c r="R39" t="n">
         <v>0</v>
@@ -37701,16 +37701,16 @@
         <v>181.8947995804632</v>
       </c>
       <c r="M41" t="n">
-        <v>213</v>
+        <v>213.4242636173429</v>
       </c>
       <c r="N41" t="n">
-        <v>103.1758960300203</v>
+        <v>207.9338608153932</v>
       </c>
       <c r="O41" t="n">
-        <v>150.7019698410586</v>
+        <v>137.7653663595904</v>
       </c>
       <c r="P41" t="n">
-        <v>90.5657124162131</v>
+        <v>0</v>
       </c>
       <c r="Q41" t="n">
         <v>0</v>
@@ -37774,19 +37774,19 @@
         <v>0</v>
       </c>
       <c r="K42" t="n">
-        <v>126.6237980382196</v>
+        <v>0</v>
       </c>
       <c r="L42" t="n">
         <v>0</v>
       </c>
       <c r="M42" t="n">
-        <v>36.18626648028518</v>
+        <v>213.4242636173429</v>
       </c>
       <c r="N42" t="n">
-        <v>213</v>
+        <v>213.4242636173429</v>
       </c>
       <c r="O42" t="n">
-        <v>213</v>
+        <v>163.6414497888537</v>
       </c>
       <c r="P42" t="n">
         <v>184.4883612256069</v>
